--- a/output/grid_api_20261013/격자기반_바다강산낙뢰_API_조사.xlsx
+++ b/output/grid_api_20261013/격자기반_바다강산낙뢰_API_조사.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="항목별 판단" sheetId="1" r:id="R4aa5a8c154654e44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 호출 산정" sheetId="2" r:id="Ra2cb1027932b413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거와 가정" sheetId="3" r:id="R57a426a456e14928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="항목별 판단" sheetId="1" r:id="R640857f49f7b46db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 호출 산정" sheetId="2" r:id="Rf84cb133cbb44ae6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거와 가정" sheetId="3" r:id="Rec23bc58b5254809"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,8 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.0"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0.000"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -81,7 +83,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -114,11 +116,23 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -337,19 +351,23 @@
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="29" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="40" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="67" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="29" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="29" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="40" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="37" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="53" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="72" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="40" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="37" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="13" customHeight="1">
@@ -370,6 +388,9 @@
       <x:c r="O1" s="2"/>
       <x:c r="P1" s="2"/>
       <x:c r="Q1" s="2"/>
+      <x:c r="R1" s="2"/>
+      <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
@@ -391,10 +412,13 @@
       <x:c r="O2" s="2"/>
       <x:c r="P2" s="2"/>
       <x:c r="Q2" s="2"/>
+      <x:c r="R2" s="2"/>
+      <x:c r="S2" s="2"/>
+      <x:c r="T2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>기준: 2026-10-13, 기상청 nx/ny 전국 원본판 149×253=37,697셀. 지점 자료는 해당 지점이 있는 격자 또는 명시한 주변 시설에만 연결한다.</x:v>
+        <x:v>기준: 2026-10-14, 기상청 nx/ny 전국 원본판 149×253=37,697셀. 지점 자료는 해당 지점이 있는 격자 또는 명시한 주변 시설에만 연결한다.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -412,6 +436,9 @@
       <x:c r="O3" s="2"/>
       <x:c r="P3" s="2"/>
       <x:c r="Q3" s="2"/>
+      <x:c r="R3" s="2"/>
+      <x:c r="S3" s="2"/>
+      <x:c r="T3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
@@ -433,6 +460,9 @@
       <x:c r="O4" s="2"/>
       <x:c r="P4" s="2"/>
       <x:c r="Q4" s="2"/>
+      <x:c r="R4" s="2"/>
+      <x:c r="S4" s="2"/>
+      <x:c r="T4" s="2"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="2"/>
@@ -452,6 +482,9 @@
       <x:c r="O5" s="2"/>
       <x:c r="P5" s="2"/>
       <x:c r="Q5" s="2"/>
+      <x:c r="R5" s="2"/>
+      <x:c r="S5" s="2"/>
+      <x:c r="T5" s="2"/>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -464,47 +497,58 @@
         <x:v>추가 상태</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>격자 적용 방식</x:v>
+        <x:v>API가 제공하는 구역</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
+        <x:v>우리격자구역(API 구역과 비교)</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
+        <x:v>구역 차이와 안내 범위</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
         <x:v>현재·지난 시간대별 안내</x:v>
       </x:c>
-      <x:c r="F6" s="7" t="str">
+      <x:c r="H6" s="7" t="str">
         <x:v>현재·지난 API 호출정보</x:v>
       </x:c>
-      <x:c r="G6" s="7" t="str">
+      <x:c r="I6" s="7" t="str">
         <x:v>관측 호출/일</x:v>
       </x:c>
-      <x:c r="H6" s="7" t="str">
+      <x:c r="J6" s="7" t="str">
         <x:v>미래 시간대별 안내</x:v>
       </x:c>
-      <x:c r="I6" s="7" t="str">
+      <x:c r="K6" s="7" t="str">
         <x:v>미래 API 호출정보</x:v>
       </x:c>
-      <x:c r="J6" s="7" t="str">
+      <x:c r="L6" s="7" t="str">
         <x:v>예보 호출/일</x:v>
       </x:c>
-      <x:c r="K6" s="7" t="str">
+      <x:c r="M6" s="7" t="str">
         <x:v>둘 다 가능 시 합계/일</x:v>
       </x:c>
-      <x:c r="L6" s="7" t="str">
-        <x:v>한도 문제</x:v>
-      </x:c>
-      <x:c r="M6" s="7" t="str">
+      <x:c r="N6" s="7" t="str">
+        <x:v>API한도</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="str">
+        <x:v>한도 결과(가능/불가능 + 이유)</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="str">
+        <x:v>운영계정 전환·증량 시</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="str">
         <x:v>제공처</x:v>
       </x:c>
-      <x:c r="N6" s="7" t="str">
+      <x:c r="R6" s="7" t="str">
         <x:v>자료 범위·표시 주의</x:v>
       </x:c>
-      <x:c r="O6" s="7" t="str">
+      <x:c r="S6" s="7" t="str">
         <x:v>추가 신청·확인</x:v>
       </x:c>
-      <x:c r="P6" s="7" t="str">
+      <x:c r="T6" s="7" t="str">
         <x:v>근거</x:v>
       </x:c>
-      <x:c r="Q6" s="2"/>
-    </x:row>
-    <x:row r="7" ht="55" customHeight="1">
+    </x:row>
+    <x:row r="7" ht="93" customHeight="1">
       <x:c r="A7" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -515,50 +559,61 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
-        <x:v>관측 지점 격자 한정; 예측 해역 격자 대응</x:v>
+        <x:v>해양관측부이 지점 좌표; ROMS 해상 예측 bbox</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str">
+        <x:v>부이 격자만 실측; ROMS는 해상 nx/ny에 재매핑</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>예: 해운대 앞바다. 우리 격자 1칸은 약 5×5km(25㎢)지만 부이 관측은 한 점이다. ROMS 해상 모델 격자도 경계가 달라 변환이 필요하며 관측·예측을 구분해 안내한다.</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
         <x:v>가능: 지점 관측 시계열</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="H7" s="8" t="str">
         <x:v>해양부이 40곳×24회; 수온·유향·유속 공유</x:v>
       </x:c>
-      <x:c r="G7" s="15" t="n">
+      <x:c r="I7" s="19" t="n">
         <x:f>'API 호출 산정'!F7</x:f>
         <x:v>960</x:v>
       </x:c>
-      <x:c r="H7" s="15" t="str">
+      <x:c r="J7" s="19" t="str">
         <x:v>가능: 모델값</x:v>
       </x:c>
-      <x:c r="I7" s="15" t="str">
+      <x:c r="K7" s="19" t="str">
         <x:v>ROMS 10해역×24미래시각 가정</x:v>
       </x:c>
-      <x:c r="J7" s="15" t="n">
+      <x:c r="L7" s="19" t="n">
         <x:f>'API 호출 산정'!F10</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K7" s="15" t="n">
-        <x:f>G7+J7</x:f>
+      <x:c r="M7" s="19" t="n">
+        <x:f>I7+L7</x:f>
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="str">
-        <x:v>KHOA 각 API 1만 회 기준 수치는 여유; bbox/용량 미검증</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="str">
+      <x:c r="N7" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O7" s="10" t="str">
+        <x:v>가능(계획): 부이 960·ROMS 240회/일, 각각 1만 회 미만. 용량 한도·bbox 분할 미검증.</x:v>
+      </x:c>
+      <x:c r="P7" s="8" t="str">
+        <x:v>현재 호출안은 개발계정 1만 회 미만. 운영계정은 심의승인·활용사례 등록 후 증량 신청 가능하지만 현재는 불필요하며 공간 범위는 동일.</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N7" s="8" t="str">
+      <x:c r="R7" s="8" t="str">
         <x:v>관측 없는 바다 격자에 관측값 생성 금지</x:v>
       </x:c>
-      <x:c r="O7" s="8" t="str">
+      <x:c r="S7" s="8" t="str">
         <x:v>부이 최신관측·ROMS 활용신청, 공간 범위 실측</x:v>
       </x:c>
-      <x:c r="P7" s="8" t="str">
-        <x:v>S2,S5</x:v>
-      </x:c>
-      <x:c r="Q7" s="2"/>
-    </x:row>
-    <x:row r="8" ht="55" customHeight="1">
+      <x:c r="T7" s="8" t="str">
+        <x:v>S2,S5,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="93" customHeight="1">
       <x:c r="A8" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -569,44 +624,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>예보지점 연안 격자 한정</x:v>
+        <x:v>연안 조석 예보 지점</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
+        <x:v>예보 지점이 속한 연안 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>예: 해운대 해변 길이는 약 1.5km로 격자 한 변 5km의 약 30%다. 예보 지점의 만·간조 시각은 그 지점 기준이며, 해변 밖이나 격자 전체에 동일하게 적용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
         <x:v>관측 극값의 시간별 API 미확인</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str">
+      <x:c r="H8" s="8" t="str">
         <x:v>관측 조위에서 극값 산출 시 별도 검증 필요</x:v>
       </x:c>
-      <x:c r="G8" s="15"/>
-      <x:c r="H8" s="15" t="str">
+      <x:c r="I8" s="19"/>
+      <x:c r="J8" s="19" t="str">
         <x:v>부분 가능: 일별 고·저조 시각 이벤트</x:v>
       </x:c>
-      <x:c r="I8" s="15" t="str">
+      <x:c r="K8" s="19" t="str">
         <x:v>예보지점 50곳×요청일 1회</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="n">
+      <x:c r="L8" s="19" t="n">
         <x:f>'API 호출 산정'!F8</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K8" s="15"/>
-      <x:c r="L8" s="10" t="str">
-        <x:v>건수상 여유; 모든 해안 격자 보장 불가</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="str">
+      <x:c r="M8" s="19"/>
+      <x:c r="N8" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O8" s="10" t="str">
+        <x:v>가능(계획): 고저조 50회/일로 1만 회 미만. 예보 지점만 제공.</x:v>
+      </x:c>
+      <x:c r="P8" s="8" t="str">
+        <x:v>현재 호출안은 개발계정 1만 회 미만. 운영계정 증량은 가능성만 안내되며 지점 부족은 해결하지 못함.</x:v>
+      </x:c>
+      <x:c r="Q8" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N8" s="8" t="str">
+      <x:c r="R8" s="8" t="str">
         <x:v>실제 만·간조와 예측 이벤트를 혼동 금지</x:v>
       </x:c>
-      <x:c r="O8" s="8" t="str">
+      <x:c r="S8" s="8" t="str">
         <x:v>고·저조 예보 활용신청, 지점-격자 매핑</x:v>
       </x:c>
-      <x:c r="P8" s="8" t="str">
-        <x:v>S3</x:v>
-      </x:c>
-      <x:c r="Q8" s="2"/>
-    </x:row>
-    <x:row r="9" ht="55" customHeight="1">
+      <x:c r="T8" s="8" t="str">
+        <x:v>S3,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="93" customHeight="1">
       <x:c r="A9" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -617,50 +683,61 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>관측소 격자 한정; 예보지점 격자 한정</x:v>
+        <x:v>조위관측소 지점; 조석 예보 지점</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
+        <x:v>관측·예보 지점이 속한 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="str">
+        <x:v>예: 해운대 연안을 기준으로 보면 조위 관측·예보는 지정 지점의 값이다. 우리 격자 1칸 약 25㎢ 안의 다른 항만·연안까지 동일 조위로 안내할 수 없다.</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
         <x:v>가능: 지점 관측 시계열</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str">
+      <x:c r="H9" s="8" t="str">
         <x:v>조위관측소 50곳×24회; 수온 등 공유</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="n">
+      <x:c r="I9" s="19" t="n">
         <x:f>'API 호출 산정'!F6</x:f>
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="H9" s="15" t="str">
+      <x:c r="J9" s="19" t="str">
         <x:v>가능: 지점 조석 시계열 예측</x:v>
       </x:c>
-      <x:c r="I9" s="15" t="str">
+      <x:c r="K9" s="19" t="str">
         <x:v>예보지점 50곳×요청일 1회</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
+      <x:c r="L9" s="19" t="n">
         <x:f>'API 호출 산정'!F9</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:f>G9+J9</x:f>
+      <x:c r="M9" s="19" t="n">
+        <x:f>I9+L9</x:f>
         <x:v>1250</x:v>
       </x:c>
-      <x:c r="L9" s="10" t="str">
-        <x:v>각 API 건수상 여유; 지점 간 보간은 별도</x:v>
-      </x:c>
-      <x:c r="M9" s="8" t="str">
+      <x:c r="N9" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O9" s="10" t="str">
+        <x:v>가능(계획): 관측 1,200·예보 50회/일, 각 API 1만 회 미만. 용량 한도 미공개.</x:v>
+      </x:c>
+      <x:c r="P9" s="8" t="str">
+        <x:v>현재 호출안은 각 개발계정 API 한도 내. 운영계정 증량 가능성은 있으나 지점 관측·예보의 공간 차이는 그대로.</x:v>
+      </x:c>
+      <x:c r="Q9" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N9" s="8" t="str">
+      <x:c r="R9" s="8" t="str">
         <x:v>관측 조위와 천문조석 예측값의 차이 존재</x:v>
       </x:c>
-      <x:c r="O9" s="8" t="str">
+      <x:c r="S9" s="8" t="str">
         <x:v>관측·시계열 예보 활용신청, 기준면 검증</x:v>
       </x:c>
-      <x:c r="P9" s="8" t="str">
-        <x:v>S1,S4</x:v>
-      </x:c>
-      <x:c r="Q9" s="2"/>
-    </x:row>
-    <x:row r="10" ht="55" customHeight="1">
+      <x:c r="T9" s="8" t="str">
+        <x:v>S1,S4,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="93" customHeight="1">
       <x:c r="A10" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -671,50 +748,61 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>부이 격자 한정; ROMS 해역 격자 대응</x:v>
+        <x:v>해양관측부이 지점; ROMS 해상 예측 bbox</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
+        <x:v>부이 격자만 실측; ROMS 해상 격자 변환</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="str">
+        <x:v>예: 해운대 앞바다를 기준으로 보면 부이 유속은 한 위치·수심의 값, 우리 격자는 약 25㎢다. ROMS 표층값을 변환해도 격자 전체의 실측 유속은 아니다.</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
         <x:v>가능: 부이 관측 시계열</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="str">
+      <x:c r="H10" s="8" t="str">
         <x:v>해양부이 40곳×24회; 수온·유향 공유</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="n">
+      <x:c r="I10" s="19" t="n">
         <x:f>'API 호출 산정'!F7</x:f>
         <x:v>960</x:v>
       </x:c>
-      <x:c r="H10" s="15" t="str">
+      <x:c r="J10" s="19" t="str">
         <x:v>가능: 표층 모델 예측</x:v>
       </x:c>
-      <x:c r="I10" s="15" t="str">
+      <x:c r="K10" s="19" t="str">
         <x:v>ROMS 10해역×24미래시각 가정</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="L10" s="19" t="n">
         <x:f>'API 호출 산정'!F10</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K10" s="15" t="n">
-        <x:f>G10+J10</x:f>
+      <x:c r="M10" s="19" t="n">
+        <x:f>I10+L10</x:f>
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="L10" s="10" t="str">
-        <x:v>건수상 여유; bbox/페이지·용량 미검증</x:v>
-      </x:c>
-      <x:c r="M10" s="8" t="str">
+      <x:c r="N10" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O10" s="10" t="str">
+        <x:v>가능(계획): 부이 960·ROMS 240회/일, 각각 1만 회 미만. 용량 한도·bbox 분할 미검증.</x:v>
+      </x:c>
+      <x:c r="P10" s="8" t="str">
+        <x:v>현재 호출안은 각 개발계정 API 한도 내. ROMS bbox·페이지 제약은 운영계정 전환만으로 해결 보장 안 됨.</x:v>
+      </x:c>
+      <x:c r="Q10" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N10" s="8" t="str">
+      <x:c r="R10" s="8" t="str">
         <x:v>조류예보 시계열은 약 200 지점의 별도 대안</x:v>
       </x:c>
-      <x:c r="O10" s="8" t="str">
+      <x:c r="S10" s="8" t="str">
         <x:v>부이·ROMS 신청, 깊이/단위 검증</x:v>
       </x:c>
-      <x:c r="P10" s="8" t="str">
-        <x:v>S2,S5,S15</x:v>
-      </x:c>
-      <x:c r="Q10" s="2"/>
-    </x:row>
-    <x:row r="11" ht="55" customHeight="1">
+      <x:c r="T10" s="8" t="str">
+        <x:v>S2,S5,S15,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="93" customHeight="1">
       <x:c r="A11" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -725,50 +813,61 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>부이 격자 한정; ROMS 해역 격자 대응</x:v>
+        <x:v>해양관측부이 지점; ROMS 해상 예측 bbox</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
+        <x:v>부이 격자만 실측; ROMS 해상 격자 변환</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>예: 해운대 앞바다를 기준으로 보면 부이 유향은 한 위치·수심의 값, 우리 격자는 약 25㎢다. ROMS 방향은 좌표·방향 기준을 맞춘 모델 예측으로만 안내한다.</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
         <x:v>가능: 부이 관측 시계열</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="str">
+      <x:c r="H11" s="8" t="str">
         <x:v>해양부이 40곳×24회; 수온·유속 공유</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="n">
+      <x:c r="I11" s="19" t="n">
         <x:f>'API 호출 산정'!F7</x:f>
         <x:v>960</x:v>
       </x:c>
-      <x:c r="H11" s="15" t="str">
+      <x:c r="J11" s="19" t="str">
         <x:v>가능: 표층 모델 예측</x:v>
       </x:c>
-      <x:c r="I11" s="15" t="str">
+      <x:c r="K11" s="19" t="str">
         <x:v>ROMS 10해역×24미래시각 가정</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="L11" s="19" t="n">
         <x:f>'API 호출 산정'!F10</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K11" s="15" t="n">
-        <x:f>G11+J11</x:f>
+      <x:c r="M11" s="19" t="n">
+        <x:f>I11+L11</x:f>
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="L11" s="10" t="str">
-        <x:v>건수상 여유; bbox/페이지·용량 미검증</x:v>
-      </x:c>
-      <x:c r="M11" s="8" t="str">
+      <x:c r="N11" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O11" s="10" t="str">
+        <x:v>가능(계획): 부이 960·ROMS 240회/일, 각각 1만 회 미만. 용량 한도·bbox 분할 미검증.</x:v>
+      </x:c>
+      <x:c r="P11" s="8" t="str">
+        <x:v>현재 호출안은 각 개발계정 API 한도 내. ROMS bbox·페이지 제약은 운영계정 전환만으로 해결 보장 안 됨.</x:v>
+      </x:c>
+      <x:c r="Q11" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N11" s="8" t="str">
+      <x:c r="R11" s="8" t="str">
         <x:v>풍향과 유향의 의미가 다름</x:v>
       </x:c>
-      <x:c r="O11" s="8" t="str">
+      <x:c r="S11" s="8" t="str">
         <x:v>부이·ROMS 신청, 방향 정의 검증</x:v>
       </x:c>
-      <x:c r="P11" s="8" t="str">
-        <x:v>S2,S5,S15</x:v>
-      </x:c>
-      <x:c r="Q11" s="2"/>
-    </x:row>
-    <x:row r="12" ht="55" customHeight="1">
+      <x:c r="T11" s="8" t="str">
+        <x:v>S2,S5,S15,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="93" customHeight="1">
       <x:c r="A12" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -779,44 +878,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>지정 해수욕장 격자만</x:v>
+        <x:v>지정 이안류 감시 해수욕장</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
+        <x:v>해수욕장 위치 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>예: 해운대 해변 약 1.5km는 격자 한 변 5km의 약 30%(길이만 비교)다. 이안류 지수는 해운대 해수욕장에만 해당하며 같은 격자의 다른 바다·해변에는 적용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
         <x:v>가능: 해수욕장 관측 시각</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="str">
+      <x:c r="H12" s="8" t="str">
         <x:v>10개 해수욕장×24회 가정</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="n">
+      <x:c r="I12" s="19" t="n">
         <x:f>'API 호출 산정'!F11</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H12" s="15" t="str">
+      <x:c r="J12" s="19" t="str">
         <x:v>공식 미래 시간별 지수 미확인</x:v>
       </x:c>
-      <x:c r="I12" s="15" t="str">
+      <x:c r="K12" s="19" t="str">
         <x:v>추정 예보로 표시하지 않음</x:v>
       </x:c>
-      <x:c r="J12" s="15"/>
-      <x:c r="K12" s="15"/>
-      <x:c r="L12" s="10" t="str">
-        <x:v>건수상 여유; 계절·대상 제한</x:v>
-      </x:c>
-      <x:c r="M12" s="8" t="str">
+      <x:c r="L12" s="19"/>
+      <x:c r="M12" s="19"/>
+      <x:c r="N12" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O12" s="10" t="str">
+        <x:v>가능(계획): 240회/일로 1만 회 미만. 감시 해수욕장·계절에 한정.</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="str">
+        <x:v>현재 호출안은 개발계정 한도 내. 운영계정 증량으로 지정 해수욕장 수나 운영기간은 늘지 않음.</x:v>
+      </x:c>
+      <x:c r="Q12" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="N12" s="8" t="str">
+      <x:c r="R12" s="8" t="str">
         <x:v>4단계 지수; 해수욕장 밖 같은 격자로 확장 금지</x:v>
       </x:c>
-      <x:c r="O12" s="8" t="str">
+      <x:c r="S12" s="8" t="str">
         <x:v>이안류 API 신청, 운영기간 확인</x:v>
       </x:c>
-      <x:c r="P12" s="8" t="str">
-        <x:v>S6</x:v>
-      </x:c>
-      <x:c r="Q12" s="2"/>
-    </x:row>
-    <x:row r="13" ht="55" customHeight="1">
+      <x:c r="T12" s="8" t="str">
+        <x:v>S6,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="93" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>바다</x:v>
       </x:c>
@@ -827,41 +937,52 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>광역 해역 보고; 격자 단위 부재</x:v>
+        <x:v>속보·주간보고의 광역 해역</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
+        <x:v>광역 해역을 5km 격자값으로 환산 불가</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="str">
+        <x:v>예: 해운대 앞바다를 약 25㎢ 격자로 나눠도 해파리 속보의 광역 해역·발견 지점은 셀 경계와 일치하지 않는다. 격자별 출현 수치로 환산하지 않고 원문 해역 범위로 안내한다.</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
         <x:v>시간별 수치 안내 불가</x:v>
       </x:c>
-      <x:c r="F13" s="8" t="str">
+      <x:c r="H13" s="8" t="str">
         <x:v>목록 4회/일 가정+신규 문서 상세. 시간별 호출에서 제외</x:v>
       </x:c>
-      <x:c r="G13" s="15"/>
-      <x:c r="H13" s="15" t="str">
+      <x:c r="I13" s="19"/>
+      <x:c r="J13" s="19" t="str">
         <x:v>시간별 예보 불가</x:v>
       </x:c>
-      <x:c r="I13" s="15" t="str">
+      <x:c r="K13" s="19" t="str">
         <x:v>주간보고의 금후전망은 정량 시간 예보 아님</x:v>
       </x:c>
-      <x:c r="J13" s="15"/>
-      <x:c r="K13" s="15"/>
-      <x:c r="L13" s="10" t="str">
-        <x:v>호출 한도 공개값 미확인; 세부 건수 가변</x:v>
-      </x:c>
-      <x:c r="M13" s="8" t="str">
+      <x:c r="L13" s="19"/>
+      <x:c r="M13" s="19"/>
+      <x:c r="N13" s="8" t="str">
+        <x:v>호출·용량 한도 공개값 미확인</x:v>
+      </x:c>
+      <x:c r="O13" s="10" t="str">
+        <x:v>판정 불가: 공식 호출·용량 한도 미확인. 시간별 격자 제공도 불가.</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="str">
+        <x:v>운영계정 구분·증량 가능 여부 공개 확인 불가. 계정 변경만으로 시간별 5km 격자 자료는 생기지 않음.</x:v>
+      </x:c>
+      <x:c r="Q13" s="8" t="str">
         <x:v>국립수산과학원</x:v>
       </x:c>
-      <x:c r="N13" s="8" t="str">
+      <x:c r="R13" s="8" t="str">
         <x:v>속보·주간보고를 지도 설명으로 제공 가능</x:v>
       </x:c>
-      <x:c r="O13" s="8" t="str">
+      <x:c r="S13" s="8" t="str">
         <x:v>NIFS API 신청, 해역 경계 해석</x:v>
       </x:c>
-      <x:c r="P13" s="8" t="str">
-        <x:v>S7</x:v>
-      </x:c>
-      <x:c r="Q13" s="2"/>
-    </x:row>
-    <x:row r="14" ht="55" customHeight="1">
+      <x:c r="T13" s="8" t="str">
+        <x:v>S7,S19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="93" customHeight="1">
       <x:c r="A14" s="8" t="str">
         <x:v>강</x:v>
       </x:c>
@@ -872,44 +993,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>수위관측소가 있는 하천 구간·격자 한정</x:v>
+        <x:v>하천 수위관측소 지점</x:v>
       </x:c>
       <x:c r="E14" s="8" t="str">
+        <x:v>관측소가 위치한 하천 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="str">
+        <x:v>예: 안동댐 방수로 관측 지점은 하천의 한 단면이다. 우리 격자 1칸은 약 5×5km(25㎢)이므로 같은 칸의 다른 지류·상하류 수위까지 대표하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
         <x:v>가능: 관측소별 시계열</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="str">
+      <x:c r="H14" s="8" t="str">
         <x:v>100관측소×24회 가정; 유량 공유</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="n">
+      <x:c r="I14" s="19" t="n">
         <x:f>'API 호출 산정'!F12</x:f>
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="H14" s="15" t="str">
+      <x:c r="J14" s="19" t="str">
         <x:v>전국 격자 시간별 공식 예보 미확인</x:v>
       </x:c>
-      <x:c r="I14" s="15" t="str">
+      <x:c r="K14" s="19" t="str">
         <x:v>홍수예보 일부 지점과 별도</x:v>
       </x:c>
-      <x:c r="J14" s="15"/>
-      <x:c r="K14" s="15"/>
-      <x:c r="L14" s="11" t="str">
-        <x:v>1만 회 기준 2,400회; 10분 갱신 시 14,400회로 초과</x:v>
-      </x:c>
-      <x:c r="M14" s="8" t="str">
+      <x:c r="L14" s="19"/>
+      <x:c r="M14" s="19"/>
+      <x:c r="N14" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O14" s="11" t="str">
+        <x:v>가능(시간별): 개발 2,400회/일&lt;1만 회. 10분안은 개발 1만 회 초과지만 운영계정 승인 한도 14,400회+재시도분이면 가능.</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="str">
+        <x:v>운영계정으로 한도 상향 신청 가능. 이 API의 운영계정 고정 횟수는 공개되지 않음. 14,400회/일+페이지·재시도분 이상 승인되면 10분 수집 가능.</x:v>
+      </x:c>
+      <x:c r="Q14" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="N14" s="8" t="str">
+      <x:c r="R14" s="8" t="str">
         <x:v>격자 안 모든 하천의 수위가 같지 않음</x:v>
       </x:c>
-      <x:c r="O14" s="8" t="str">
+      <x:c r="S14" s="8" t="str">
         <x:v>우량수위 API 신청, 지점목록 확정</x:v>
       </x:c>
-      <x:c r="P14" s="8" t="str">
-        <x:v>S8</x:v>
-      </x:c>
-      <x:c r="Q14" s="2"/>
-    </x:row>
-    <x:row r="15" ht="55" customHeight="1">
+      <x:c r="T14" s="8" t="str">
+        <x:v>S8,S21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="93" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>강</x:v>
       </x:c>
@@ -920,44 +1052,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
-        <x:v>유량 관측소가 있는 하천 구간·격자 한정</x:v>
+        <x:v>하천 유량관측소 지점</x:v>
       </x:c>
       <x:c r="E15" s="8" t="str">
+        <x:v>관측소가 위치한 하천 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="str">
+        <x:v>예: 안동댐 방수로 지점의 유량은 해당 하천 단면을 통과하는 양이다. 우리 격자 약 25㎢ 전체나 같은 칸의 다른 하천 유량으로 확장할 수 없다.</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
         <x:v>가능: 관측소별 시계열</x:v>
       </x:c>
-      <x:c r="F15" s="8" t="str">
+      <x:c r="H15" s="8" t="str">
         <x:v>100관측소×24회 가정; 수위 공유</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="n">
+      <x:c r="I15" s="19" t="n">
         <x:f>'API 호출 산정'!F12</x:f>
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="H15" s="15" t="str">
+      <x:c r="J15" s="19" t="str">
         <x:v>전국 격자 시간별 공식 예보 미확인</x:v>
       </x:c>
-      <x:c r="I15" s="15" t="str">
+      <x:c r="K15" s="19" t="str">
         <x:v>홍수예보 일부 지점과 별도</x:v>
       </x:c>
-      <x:c r="J15" s="15"/>
-      <x:c r="K15" s="15"/>
-      <x:c r="L15" s="11" t="str">
-        <x:v>1만 회 기준 2,400회; 10분 갱신 시 14,400회로 초과</x:v>
-      </x:c>
-      <x:c r="M15" s="8" t="str">
+      <x:c r="L15" s="19"/>
+      <x:c r="M15" s="19"/>
+      <x:c r="N15" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O15" s="11" t="str">
+        <x:v>가능(시간별): 개발 2,400회/일&lt;1만 회. 10분안은 개발 1만 회 초과지만 운영계정 승인 한도 14,400회+재시도분이면 가능.</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="str">
+        <x:v>운영계정으로 한도 상향 신청 가능. 이 API의 운영계정 고정 횟수는 공개되지 않음. 14,400회/일+페이지·재시도분 이상 승인되면 10분 수집 가능.</x:v>
+      </x:c>
+      <x:c r="Q15" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="N15" s="8" t="str">
+      <x:c r="R15" s="8" t="str">
         <x:v>유량은 하천 단면의 값; 면적 전체값 아님</x:v>
       </x:c>
-      <x:c r="O15" s="8" t="str">
+      <x:c r="S15" s="8" t="str">
         <x:v>우량수위 API 신청, 관측소 좌표/하천 연결</x:v>
       </x:c>
-      <x:c r="P15" s="8" t="str">
-        <x:v>S8</x:v>
-      </x:c>
-      <x:c r="Q15" s="2"/>
-    </x:row>
-    <x:row r="16" ht="55" customHeight="1">
+      <x:c r="T15" s="8" t="str">
+        <x:v>S8,S21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="93" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>강</x:v>
       </x:c>
@@ -968,44 +1111,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
-        <x:v>댐 시설 격자 또는 저수지 위치 한정</x:v>
+        <x:v>K-water 댐·보 시설 지점</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str">
+        <x:v>댐 시설 위치 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>예: 안동댐 수위는 댐 시설·저수지의 값이다. 우리 격자 약 25㎢와 범위가 다르고 저수지가 여러 칸에 걸쳐도 각 칸의 지형 높이가 같은 뜻은 아니다.</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="str">
         <x:v>가능: 댐별 시계열</x:v>
       </x:c>
-      <x:c r="F16" s="8" t="str">
+      <x:c r="H16" s="8" t="str">
         <x:v>61댐·보×24회; 유입·방류 공유</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="n">
+      <x:c r="I16" s="19" t="n">
         <x:f>'API 호출 산정'!F13</x:f>
         <x:v>1464</x:v>
       </x:c>
-      <x:c r="H16" s="15" t="str">
+      <x:c r="J16" s="19" t="str">
         <x:v>공식 전국 시간별 예보 미확인</x:v>
       </x:c>
-      <x:c r="I16" s="15" t="str">
+      <x:c r="K16" s="19" t="str">
         <x:v>운영계획은 실제 수위 예보와 구분</x:v>
       </x:c>
-      <x:c r="J16" s="15"/>
-      <x:c r="K16" s="15"/>
-      <x:c r="L16" s="10" t="str">
-        <x:v>1만 회 기준 1,464회; 10분 갱신은 8,784회</x:v>
-      </x:c>
-      <x:c r="M16" s="8" t="str">
+      <x:c r="L16" s="19"/>
+      <x:c r="M16" s="19"/>
+      <x:c r="N16" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O16" s="10" t="str">
+        <x:v>가능(시간별): 1,464회/일&lt;1만 회. 10분별 61곳은 8,784회로 재시도 여유 작음.</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="str">
+        <x:v>시간별 1,464회, 10분별 8,784회로 개발계정 1만 회 이내. 운영계정 전환은 필수 아님; 재시도 증가 시 증량 검토.</x:v>
+      </x:c>
+      <x:c r="Q16" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="N16" s="8" t="str">
+      <x:c r="R16" s="8" t="str">
         <x:v>61개 댐·보 범위; 모든 댐 아님</x:v>
       </x:c>
-      <x:c r="O16" s="8" t="str">
+      <x:c r="S16" s="8" t="str">
         <x:v>수문 운영 API 신청, 시설 좌표 매핑</x:v>
       </x:c>
-      <x:c r="P16" s="8" t="str">
-        <x:v>S9</x:v>
-      </x:c>
-      <x:c r="Q16" s="2"/>
-    </x:row>
-    <x:row r="17" ht="55" customHeight="1">
+      <x:c r="T16" s="8" t="str">
+        <x:v>S9,S21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="93" customHeight="1">
       <x:c r="A17" s="8" t="str">
         <x:v>강</x:v>
       </x:c>
@@ -1016,44 +1170,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>댐 시설·하류 영향 구간 별도</x:v>
+        <x:v>K-water 댐·보 시설 지점</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
+        <x:v>댐 시설 격자와 하류 영향구역은 별개</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str">
+        <x:v>예: 안동댐 방류량은 댐 출구의 값이다. 우리 격자 한 칸 약 25㎢로 하류 영향 범위를 정할 수 없으며 하천 연결·이동시간이 필요하다.</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="str">
         <x:v>가능: 댐별 시계열</x:v>
       </x:c>
-      <x:c r="F17" s="8" t="str">
+      <x:c r="H17" s="8" t="str">
         <x:v>61댐·보×24회; 수위·유입 공유</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="n">
+      <x:c r="I17" s="19" t="n">
         <x:f>'API 호출 산정'!F13</x:f>
         <x:v>1464</x:v>
       </x:c>
-      <x:c r="H17" s="15" t="str">
+      <x:c r="J17" s="19" t="str">
         <x:v>확정 방류계획의 시간별 API 미확인</x:v>
       </x:c>
-      <x:c r="I17" s="15" t="str">
+      <x:c r="K17" s="19" t="str">
         <x:v>예정 방류와 실제 방류를 구분</x:v>
       </x:c>
-      <x:c r="J17" s="15"/>
-      <x:c r="K17" s="15"/>
-      <x:c r="L17" s="10" t="str">
-        <x:v>1만 회 기준 1,464회; 10분 갱신은 8,784회</x:v>
-      </x:c>
-      <x:c r="M17" s="8" t="str">
+      <x:c r="L17" s="19"/>
+      <x:c r="M17" s="19"/>
+      <x:c r="N17" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O17" s="10" t="str">
+        <x:v>가능(시간별): 1,464회/일&lt;1만 회. 10분별 61곳은 8,784회로 재시도 여유 작음.</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="str">
+        <x:v>시간별 1,464회, 10분별 8,784회로 개발계정 1만 회 이내. 운영계정 전환은 필수 아님; 재시도 증가 시 증량 검토.</x:v>
+      </x:c>
+      <x:c r="Q17" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="N17" s="8" t="str">
+      <x:c r="R17" s="8" t="str">
         <x:v>댐 위치 격자만으로 하류 영향 판정 불가</x:v>
       </x:c>
-      <x:c r="O17" s="8" t="str">
+      <x:c r="S17" s="8" t="str">
         <x:v>수문 운영 API 신청, 방류 공지 별도 조사</x:v>
       </x:c>
-      <x:c r="P17" s="8" t="str">
-        <x:v>S9</x:v>
-      </x:c>
-      <x:c r="Q17" s="2"/>
-    </x:row>
-    <x:row r="18" ht="55" customHeight="1">
+      <x:c r="T17" s="8" t="str">
+        <x:v>S9,S21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="93" customHeight="1">
       <x:c r="A18" s="8" t="str">
         <x:v>강</x:v>
       </x:c>
@@ -1064,44 +1229,55 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
-        <x:v>댐 시설 격자 한정</x:v>
+        <x:v>K-water 댐·보 시설 지점</x:v>
       </x:c>
       <x:c r="E18" s="8" t="str">
+        <x:v>댐 시설 위치 격자만 연결</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
+        <x:v>예: 안동댐 유입량은 상류에서 댐으로 모이는 집계값이다. 우리 격자 한 칸 약 25㎢의 유량으로 나눌 수 없다.</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
         <x:v>가능: 댐별 시계열</x:v>
       </x:c>
-      <x:c r="F18" s="8" t="str">
+      <x:c r="H18" s="8" t="str">
         <x:v>61댐·보×24회; 수위·방류 공유</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="n">
+      <x:c r="I18" s="19" t="n">
         <x:f>'API 호출 산정'!F13</x:f>
         <x:v>1464</x:v>
       </x:c>
-      <x:c r="H18" s="15" t="str">
+      <x:c r="J18" s="19" t="str">
         <x:v>공식 전국 시간별 예보 미확인</x:v>
       </x:c>
-      <x:c r="I18" s="15" t="str">
+      <x:c r="K18" s="19" t="str">
         <x:v>모델 추정치 임의 사용 금지</x:v>
       </x:c>
-      <x:c r="J18" s="15"/>
-      <x:c r="K18" s="15"/>
-      <x:c r="L18" s="10" t="str">
-        <x:v>1만 회 기준 1,464회; 10분 갱신은 8,784회</x:v>
-      </x:c>
-      <x:c r="M18" s="8" t="str">
+      <x:c r="L18" s="19"/>
+      <x:c r="M18" s="19"/>
+      <x:c r="N18" s="8" t="str">
+        <x:v>해당 API 개발계정 10,000회/일; 운영계정 증량 가능(고정 숫자 미공개); 용량 한도 미공개</x:v>
+      </x:c>
+      <x:c r="O18" s="10" t="str">
+        <x:v>가능(시간별): 1,464회/일&lt;1만 회. 10분별 61곳은 8,784회로 재시도 여유 작음.</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="str">
+        <x:v>시간별 1,464회, 10분별 8,784회로 개발계정 1만 회 이내. 운영계정 전환은 필수 아님; 재시도 증가 시 증량 검토.</x:v>
+      </x:c>
+      <x:c r="Q18" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="N18" s="8" t="str">
+      <x:c r="R18" s="8" t="str">
         <x:v>유입량은 운영 자료의 계산값</x:v>
       </x:c>
-      <x:c r="O18" s="8" t="str">
+      <x:c r="S18" s="8" t="str">
         <x:v>수문 운영 API 신청, 단위 확인</x:v>
       </x:c>
-      <x:c r="P18" s="8" t="str">
-        <x:v>S9</x:v>
-      </x:c>
-      <x:c r="Q18" s="2"/>
-    </x:row>
-    <x:row r="19" ht="55" customHeight="1">
+      <x:c r="T18" s="8" t="str">
+        <x:v>S9,S21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="93" customHeight="1">
       <x:c r="A19" s="8" t="str">
         <x:v>산</x:v>
       </x:c>
@@ -1112,41 +1288,52 @@
         <x:v>제외 확정</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
-        <x:v>KIM 모델 격자는 앱 지상 nx/ny와 좌표 변환 필요</x:v>
+        <x:v>윈드프로파일러 지점; KIM 모델 자체 격자</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str">
+        <x:v>지점·모델 격자와 nx/ny 불일치; 도입 제외</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="str">
+        <x:v>예: 설악산 대청봉은 해발 1,708m, 우리 지상 격자는 약 25㎢다. 고층관측은 다른 지점·높이의 점 자료, KIM은 별도 3차원 격자여서 정상 바람으로 바로 안내할 수 없다(도입 제외).</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
         <x:v>윈드프로파일러는 10분 지점 관측; 전 격자 시간별 아님</x:v>
       </x:c>
-      <x:c r="F19" s="8" t="str">
+      <x:c r="H19" s="8" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="G19" s="15"/>
-      <x:c r="H19" s="15" t="str">
+      <x:c r="I19" s="19"/>
+      <x:c r="J19" s="19" t="str">
         <x:v>KIM 3차원 모델 후보이나 제외</x:v>
       </x:c>
-      <x:c r="I19" s="15" t="str">
+      <x:c r="K19" s="19" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="J19" s="15"/>
-      <x:c r="K19" s="15"/>
-      <x:c r="L19" s="10" t="str">
-        <x:v>APIHub 용량 부담으로 도입 제외</x:v>
-      </x:c>
-      <x:c r="M19" s="8" t="str">
+      <x:c r="L19" s="19"/>
+      <x:c r="M19" s="19"/>
+      <x:c r="N19" s="8" t="str">
+        <x:v>APIHub 일반회원 공식 20,000회·5GB/일</x:v>
+      </x:c>
+      <x:c r="O19" s="10" t="str">
+        <x:v>도입 제외: 추가 호출·용량 0. 후보 API의 용량은 산정 대상 아님.</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="str">
+        <x:v>도입 제외. 공공데이터포털 운영계정과 APIHub 회원 구분은 별개이며 계정 변경을 검토할 대상 아님.</x:v>
+      </x:c>
+      <x:c r="Q19" s="8" t="str">
         <x:v>기상청 APIHub</x:v>
       </x:c>
-      <x:c r="N19" s="8" t="str">
+      <x:c r="R19" s="8" t="str">
         <x:v>레윈존데 정기 관측은 하루 2회; 산의 임의 고도 실측 아님</x:v>
       </x:c>
-      <x:c r="O19" s="8" t="str">
+      <x:c r="S19" s="8" t="str">
         <x:v>현재 신청 대상 아님</x:v>
       </x:c>
-      <x:c r="P19" s="8" t="str">
-        <x:v>S10,S11</x:v>
-      </x:c>
-      <x:c r="Q19" s="2"/>
-    </x:row>
-    <x:row r="20" ht="55" customHeight="1">
+      <x:c r="T19" s="8" t="str">
+        <x:v>S10,S11,S20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="93" customHeight="1">
       <x:c r="A20" s="8" t="str">
         <x:v>산</x:v>
       </x:c>
@@ -1157,41 +1344,52 @@
         <x:v>제외 확정</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
-        <x:v>ASOS 최저운고는 관측소 지점값</x:v>
+        <x:v>ASOS 관측소 지점</x:v>
       </x:c>
       <x:c r="E20" s="8" t="str">
+        <x:v>관측소 격자만 실측; 도입 제외</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="str">
+        <x:v>예: 대청봉 1,708m와 속초 ASOS 관측소 약 18m는 높이만 약 1,690m 차이 난다. 최저운고는 속초 관측점 기준이고 대청봉 주변 약 25㎢의 구름 높이가 아니다(도입 제외).</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="str">
         <x:v>지점 관측 가능; 전 산악 격자 시간별 아님</x:v>
       </x:c>
-      <x:c r="F20" s="8" t="str">
+      <x:c r="H20" s="8" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="G20" s="15"/>
-      <x:c r="H20" s="15" t="str">
+      <x:c r="I20" s="19"/>
+      <x:c r="J20" s="19" t="str">
         <x:v>같은 의미의 격자 미래 API 검증 안 됨</x:v>
       </x:c>
-      <x:c r="I20" s="15" t="str">
+      <x:c r="K20" s="19" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="J20" s="15"/>
-      <x:c r="K20" s="15"/>
-      <x:c r="L20" s="10" t="str">
-        <x:v>APIHub 용량 부담으로 도입 제외</x:v>
-      </x:c>
-      <x:c r="M20" s="8" t="str">
+      <x:c r="L20" s="19"/>
+      <x:c r="M20" s="19"/>
+      <x:c r="N20" s="8" t="str">
+        <x:v>APIHub 일반회원 공식 20,000회·5GB/일</x:v>
+      </x:c>
+      <x:c r="O20" s="10" t="str">
+        <x:v>도입 제외: 추가 호출·용량 0. 후보 API의 용량은 산정 대상 아님.</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="str">
+        <x:v>도입 제외. 공공데이터포털 운영계정과 APIHub 회원 구분은 별개이며 계정 변경을 검토할 대상 아님.</x:v>
+      </x:c>
+      <x:c r="Q20" s="8" t="str">
         <x:v>기상청 APIHub</x:v>
       </x:c>
-      <x:c r="N20" s="8" t="str">
+      <x:c r="R20" s="8" t="str">
         <x:v>레이더 에코상단 고도는 최저운고가 아님</x:v>
       </x:c>
-      <x:c r="O20" s="8" t="str">
+      <x:c r="S20" s="8" t="str">
         <x:v>현재 신청 대상 아님</x:v>
       </x:c>
-      <x:c r="P20" s="8" t="str">
-        <x:v>S12</x:v>
-      </x:c>
-      <x:c r="Q20" s="2"/>
-    </x:row>
-    <x:row r="21" ht="55" customHeight="1">
+      <x:c r="T20" s="8" t="str">
+        <x:v>S12,S20,S22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="93" customHeight="1">
       <x:c r="A21" s="8" t="str">
         <x:v>산</x:v>
       </x:c>
@@ -1202,41 +1400,52 @@
         <x:v>제외 확정</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
-        <x:v>ASOS 전운량은 관측소 지점값</x:v>
+        <x:v>ASOS 관측소 지점; KIM 모델 자체 격자</x:v>
       </x:c>
       <x:c r="E21" s="8" t="str">
+        <x:v>지점·모델 격자와 nx/ny 불일치; 도입 제외</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="str">
+        <x:v>예: 대청봉 1,708m와 속초 ASOS 관측소 약 18m는 높이만 약 1,690m 차이 난다. 전운량은 속초 관측점 하늘의 비율이므로 대청봉 격자 약 25㎢ 전체의 실측 운량이 아니다(도입 제외).</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="str">
         <x:v>지점 관측 가능; 전 산악 격자 시간별 아님</x:v>
       </x:c>
-      <x:c r="F21" s="8" t="str">
+      <x:c r="H21" s="8" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="G21" s="15"/>
-      <x:c r="H21" s="15" t="str">
+      <x:c r="I21" s="19"/>
+      <x:c r="J21" s="19" t="str">
         <x:v>KIM 전운량 모델 후보이나 제외</x:v>
       </x:c>
-      <x:c r="I21" s="15" t="str">
+      <x:c r="K21" s="19" t="str">
         <x:v>제외 결정으로 추가 호출 0</x:v>
       </x:c>
-      <x:c r="J21" s="15"/>
-      <x:c r="K21" s="15"/>
-      <x:c r="L21" s="10" t="str">
-        <x:v>APIHub 용량 부담으로 도입 제외</x:v>
-      </x:c>
-      <x:c r="M21" s="8" t="str">
+      <x:c r="L21" s="19"/>
+      <x:c r="M21" s="19"/>
+      <x:c r="N21" s="8" t="str">
+        <x:v>APIHub 일반회원 공식 20,000회·5GB/일</x:v>
+      </x:c>
+      <x:c r="O21" s="10" t="str">
+        <x:v>도입 제외: 추가 호출·용량 0. 후보 API의 용량은 산정 대상 아님.</x:v>
+      </x:c>
+      <x:c r="P21" s="8" t="str">
+        <x:v>도입 제외. 공공데이터포털 운영계정과 APIHub 회원 구분은 별개이며 계정 변경을 검토할 대상 아님.</x:v>
+      </x:c>
+      <x:c r="Q21" s="8" t="str">
         <x:v>기상청 APIHub</x:v>
       </x:c>
-      <x:c r="N21" s="8" t="str">
+      <x:c r="R21" s="8" t="str">
         <x:v>기존 SKY는 맑음·구름많음·흐림 범주</x:v>
       </x:c>
-      <x:c r="O21" s="8" t="str">
+      <x:c r="S21" s="8" t="str">
         <x:v>현재 신청 대상 아님</x:v>
       </x:c>
-      <x:c r="P21" s="8" t="str">
-        <x:v>S11,S12</x:v>
-      </x:c>
-      <x:c r="Q21" s="2"/>
-    </x:row>
-    <x:row r="22" ht="55" customHeight="1">
+      <x:c r="T21" s="8" t="str">
+        <x:v>S11,S12,S20,S22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="93" customHeight="1">
       <x:c r="A22" s="8" t="str">
         <x:v>그외</x:v>
       </x:c>
@@ -1247,42 +1456,53 @@
         <x:v>검토</x:v>
       </x:c>
       <x:c r="D22" s="8" t="str">
-        <x:v>전국 낙뢰 좌표를 발생 위치 nx/ny에 배정</x:v>
+        <x:v>전국 낙뢰 발생 좌표</x:v>
       </x:c>
       <x:c r="E22" s="8" t="str">
+        <x:v>낙뢰 좌표를 발생 위치 nx/ny로 변환</x:v>
+      </x:c>
+      <x:c r="F22" s="8" t="str">
+        <x:v>API는 개별 발생 좌표를 주므로 우리 격자별 발생 이력은 집계 가능하다. 다만 격자 전체 낙뢰 위험도나 미래 발생 예보를 뜻하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="str">
         <x:v>가능: 관측 좌표·시각</x:v>
       </x:c>
-      <x:c r="F22" s="8" t="str">
+      <x:c r="H22" s="8" t="str">
         <x:v>전국 원시자료 10분마다 1회; 지역별 호출 안 함</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="n">
+      <x:c r="I22" s="19" t="n">
         <x:f>'API 호출 산정'!F14</x:f>
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H22" s="15" t="str">
+      <x:c r="J22" s="19" t="str">
         <x:v>공식 격자별 시간대 예보 미확인</x:v>
       </x:c>
-      <x:c r="I22" s="15" t="str">
+      <x:c r="K22" s="19" t="str">
         <x:v>발생 위치 관측을 미래 발생 예보로 표시 금지</x:v>
       </x:c>
-      <x:c r="J22" s="15"/>
-      <x:c r="K22" s="15"/>
-      <x:c r="L22" s="9" t="str">
-        <x:v>호출 144회는 여유; 응답 바이트·실제 잔여 4.5GB 확인 필요</x:v>
-      </x:c>
-      <x:c r="M22" s="8" t="str">
+      <x:c r="L22" s="19"/>
+      <x:c r="M22" s="19"/>
+      <x:c r="N22" s="8" t="str">
+        <x:v>APIHub 일반회원 공식 20,000회·5GB/일</x:v>
+      </x:c>
+      <x:c r="O22" s="9" t="str">
+        <x:v>가능(공식 한도): 2MB/회 가정도 겨울 합산 4.53GB&lt;APIHub 5GB. 144회/일 호출도 2만 회 내. 실제 평균 약 5.264MB/회 초과 시 용량 초과.</x:v>
+      </x:c>
+      <x:c r="P22" s="8" t="str">
+        <x:v>공공데이터포털 운영계정 전환 불필요. 2MB/회 가정의 4.53GB/일은 APIHub 일반회원 공식 5GB/일 이내. 실제 바이트 확인 후 공식 한도와 비교; 기관회원 신청은 현재 계산상 불필요.</x:v>
+      </x:c>
+      <x:c r="Q22" s="8" t="str">
         <x:v>기상청 APIHub</x:v>
       </x:c>
-      <x:c r="N22" s="8" t="str">
+      <x:c r="R22" s="8" t="str">
         <x:v>이전 행정구역 횟수 API 24회/일 산정은 격자 요구에 부적합</x:v>
       </x:c>
-      <x:c r="O22" s="8" t="str">
+      <x:c r="S22" s="8" t="str">
         <x:v>낙뢰관측 활용신청, 용량 실측·결측 점검</x:v>
       </x:c>
-      <x:c r="P22" s="8" t="str">
-        <x:v>S13,S14</x:v>
-      </x:c>
-      <x:c r="Q22" s="2"/>
+      <x:c r="T22" s="8" t="str">
+        <x:v>S13,S14,S18</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2"/>
@@ -1302,6 +1522,9 @@
       <x:c r="O23" s="2"/>
       <x:c r="P23" s="2"/>
       <x:c r="Q23" s="2"/>
+      <x:c r="R23" s="2"/>
+      <x:c r="S23" s="2"/>
+      <x:c r="T23" s="2"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2"/>
@@ -1321,6 +1544,9 @@
       <x:c r="O24" s="2"/>
       <x:c r="P24" s="2"/>
       <x:c r="Q24" s="2"/>
+      <x:c r="R24" s="2"/>
+      <x:c r="S24" s="2"/>
+      <x:c r="T24" s="2"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="str">
@@ -1342,10 +1568,13 @@
       <x:c r="O25" s="2"/>
       <x:c r="P25" s="2"/>
       <x:c r="Q25" s="2"/>
+      <x:c r="R25" s="2"/>
+      <x:c r="S25" s="2"/>
+      <x:c r="T25" s="2"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="2" t="str">
-        <x:v>한도 판정은 호출 건수 기준 예시다. 별도 승인 상태, 실제 응답 크기, API 페이지 수, 재시도, 현행 다른 기능 사용량은 미확인이다.</x:v>
+        <x:v>한도 판정은 제공처 공식 한도와 저장소의 겨울 계획 예산을 사용하며 서버 내부 보호선은 제외한다. 운영계정 고정 한도와 실제 승인량, 응답 KB는 미확인이다.</x:v>
       </x:c>
       <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
@@ -1363,6 +1592,9 @@
       <x:c r="O26" s="2"/>
       <x:c r="P26" s="2"/>
       <x:c r="Q26" s="2"/>
+      <x:c r="R26" s="2"/>
+      <x:c r="S26" s="2"/>
+      <x:c r="T26" s="2"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2"/>
@@ -1382,6 +1614,9 @@
       <x:c r="O27" s="2"/>
       <x:c r="P27" s="2"/>
       <x:c r="Q27" s="2"/>
+      <x:c r="R27" s="2"/>
+      <x:c r="S27" s="2"/>
+      <x:c r="T27" s="2"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2"/>
@@ -1401,6 +1636,9 @@
       <x:c r="O28" s="2"/>
       <x:c r="P28" s="2"/>
       <x:c r="Q28" s="2"/>
+      <x:c r="R28" s="2"/>
+      <x:c r="S28" s="2"/>
+      <x:c r="T28" s="2"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2"/>
@@ -1420,6 +1658,9 @@
       <x:c r="O29" s="2"/>
       <x:c r="P29" s="2"/>
       <x:c r="Q29" s="2"/>
+      <x:c r="R29" s="2"/>
+      <x:c r="S29" s="2"/>
+      <x:c r="T29" s="2"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2"/>
@@ -1439,6 +1680,9 @@
       <x:c r="O30" s="2"/>
       <x:c r="P30" s="2"/>
       <x:c r="Q30" s="2"/>
+      <x:c r="R30" s="2"/>
+      <x:c r="S30" s="2"/>
+      <x:c r="T30" s="2"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2"/>
@@ -1458,6 +1702,9 @@
       <x:c r="O31" s="2"/>
       <x:c r="P31" s="2"/>
       <x:c r="Q31" s="2"/>
+      <x:c r="R31" s="2"/>
+      <x:c r="S31" s="2"/>
+      <x:c r="T31" s="2"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2"/>
@@ -1477,6 +1724,9 @@
       <x:c r="O32" s="2"/>
       <x:c r="P32" s="2"/>
       <x:c r="Q32" s="2"/>
+      <x:c r="R32" s="2"/>
+      <x:c r="S32" s="2"/>
+      <x:c r="T32" s="2"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2"/>
@@ -1496,6 +1746,9 @@
       <x:c r="O33" s="2"/>
       <x:c r="P33" s="2"/>
       <x:c r="Q33" s="2"/>
+      <x:c r="R33" s="2"/>
+      <x:c r="S33" s="2"/>
+      <x:c r="T33" s="2"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2"/>
@@ -1515,6 +1768,9 @@
       <x:c r="O34" s="2"/>
       <x:c r="P34" s="2"/>
       <x:c r="Q34" s="2"/>
+      <x:c r="R34" s="2"/>
+      <x:c r="S34" s="2"/>
+      <x:c r="T34" s="2"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2"/>
@@ -1534,6 +1790,9 @@
       <x:c r="O35" s="2"/>
       <x:c r="P35" s="2"/>
       <x:c r="Q35" s="2"/>
+      <x:c r="R35" s="2"/>
+      <x:c r="S35" s="2"/>
+      <x:c r="T35" s="2"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2"/>
@@ -1553,6 +1812,9 @@
       <x:c r="O36" s="2"/>
       <x:c r="P36" s="2"/>
       <x:c r="Q36" s="2"/>
+      <x:c r="R36" s="2"/>
+      <x:c r="S36" s="2"/>
+      <x:c r="T36" s="2"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2"/>
@@ -1572,6 +1834,9 @@
       <x:c r="O37" s="2"/>
       <x:c r="P37" s="2"/>
       <x:c r="Q37" s="2"/>
+      <x:c r="R37" s="2"/>
+      <x:c r="S37" s="2"/>
+      <x:c r="T37" s="2"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2"/>
@@ -1591,6 +1856,9 @@
       <x:c r="O38" s="2"/>
       <x:c r="P38" s="2"/>
       <x:c r="Q38" s="2"/>
+      <x:c r="R38" s="2"/>
+      <x:c r="S38" s="2"/>
+      <x:c r="T38" s="2"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2"/>
@@ -1610,6 +1878,9 @@
       <x:c r="O39" s="2"/>
       <x:c r="P39" s="2"/>
       <x:c r="Q39" s="2"/>
+      <x:c r="R39" s="2"/>
+      <x:c r="S39" s="2"/>
+      <x:c r="T39" s="2"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="2"/>
@@ -1629,6 +1900,9 @@
       <x:c r="O40" s="2"/>
       <x:c r="P40" s="2"/>
       <x:c r="Q40" s="2"/>
+      <x:c r="R40" s="2"/>
+      <x:c r="S40" s="2"/>
+      <x:c r="T40" s="2"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2"/>
@@ -1648,6 +1922,9 @@
       <x:c r="O41" s="2"/>
       <x:c r="P41" s="2"/>
       <x:c r="Q41" s="2"/>
+      <x:c r="R41" s="2"/>
+      <x:c r="S41" s="2"/>
+      <x:c r="T41" s="2"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2"/>
@@ -1667,6 +1944,9 @@
       <x:c r="O42" s="2"/>
       <x:c r="P42" s="2"/>
       <x:c r="Q42" s="2"/>
+      <x:c r="R42" s="2"/>
+      <x:c r="S42" s="2"/>
+      <x:c r="T42" s="2"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2"/>
@@ -1686,6 +1966,9 @@
       <x:c r="O43" s="2"/>
       <x:c r="P43" s="2"/>
       <x:c r="Q43" s="2"/>
+      <x:c r="R43" s="2"/>
+      <x:c r="S43" s="2"/>
+      <x:c r="T43" s="2"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2"/>
@@ -1705,6 +1988,9 @@
       <x:c r="O44" s="2"/>
       <x:c r="P44" s="2"/>
       <x:c r="Q44" s="2"/>
+      <x:c r="R44" s="2"/>
+      <x:c r="S44" s="2"/>
+      <x:c r="T44" s="2"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2"/>
@@ -1724,6 +2010,9 @@
       <x:c r="O45" s="2"/>
       <x:c r="P45" s="2"/>
       <x:c r="Q45" s="2"/>
+      <x:c r="R45" s="2"/>
+      <x:c r="S45" s="2"/>
+      <x:c r="T45" s="2"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2"/>
@@ -1743,6 +2032,9 @@
       <x:c r="O46" s="2"/>
       <x:c r="P46" s="2"/>
       <x:c r="Q46" s="2"/>
+      <x:c r="R46" s="2"/>
+      <x:c r="S46" s="2"/>
+      <x:c r="T46" s="2"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2"/>
@@ -1762,6 +2054,9 @@
       <x:c r="O47" s="2"/>
       <x:c r="P47" s="2"/>
       <x:c r="Q47" s="2"/>
+      <x:c r="R47" s="2"/>
+      <x:c r="S47" s="2"/>
+      <x:c r="T47" s="2"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2"/>
@@ -1781,6 +2076,9 @@
       <x:c r="O48" s="2"/>
       <x:c r="P48" s="2"/>
       <x:c r="Q48" s="2"/>
+      <x:c r="R48" s="2"/>
+      <x:c r="S48" s="2"/>
+      <x:c r="T48" s="2"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2"/>
@@ -1800,6 +2098,9 @@
       <x:c r="O49" s="2"/>
       <x:c r="P49" s="2"/>
       <x:c r="Q49" s="2"/>
+      <x:c r="R49" s="2"/>
+      <x:c r="S49" s="2"/>
+      <x:c r="T49" s="2"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2"/>
@@ -1819,6 +2120,9 @@
       <x:c r="O50" s="2"/>
       <x:c r="P50" s="2"/>
       <x:c r="Q50" s="2"/>
+      <x:c r="R50" s="2"/>
+      <x:c r="S50" s="2"/>
+      <x:c r="T50" s="2"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2"/>
@@ -1838,6 +2142,9 @@
       <x:c r="O51" s="2"/>
       <x:c r="P51" s="2"/>
       <x:c r="Q51" s="2"/>
+      <x:c r="R51" s="2"/>
+      <x:c r="S51" s="2"/>
+      <x:c r="T51" s="2"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2"/>
@@ -1857,6 +2164,9 @@
       <x:c r="O52" s="2"/>
       <x:c r="P52" s="2"/>
       <x:c r="Q52" s="2"/>
+      <x:c r="R52" s="2"/>
+      <x:c r="S52" s="2"/>
+      <x:c r="T52" s="2"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2"/>
@@ -1876,6 +2186,9 @@
       <x:c r="O53" s="2"/>
       <x:c r="P53" s="2"/>
       <x:c r="Q53" s="2"/>
+      <x:c r="R53" s="2"/>
+      <x:c r="S53" s="2"/>
+      <x:c r="T53" s="2"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2"/>
@@ -1895,6 +2208,9 @@
       <x:c r="O54" s="2"/>
       <x:c r="P54" s="2"/>
       <x:c r="Q54" s="2"/>
+      <x:c r="R54" s="2"/>
+      <x:c r="S54" s="2"/>
+      <x:c r="T54" s="2"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2"/>
@@ -1914,6 +2230,9 @@
       <x:c r="O55" s="2"/>
       <x:c r="P55" s="2"/>
       <x:c r="Q55" s="2"/>
+      <x:c r="R55" s="2"/>
+      <x:c r="S55" s="2"/>
+      <x:c r="T55" s="2"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2"/>
@@ -1933,6 +2252,9 @@
       <x:c r="O56" s="2"/>
       <x:c r="P56" s="2"/>
       <x:c r="Q56" s="2"/>
+      <x:c r="R56" s="2"/>
+      <x:c r="S56" s="2"/>
+      <x:c r="T56" s="2"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2"/>
@@ -1952,6 +2274,9 @@
       <x:c r="O57" s="2"/>
       <x:c r="P57" s="2"/>
       <x:c r="Q57" s="2"/>
+      <x:c r="R57" s="2"/>
+      <x:c r="S57" s="2"/>
+      <x:c r="T57" s="2"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2"/>
@@ -1971,6 +2296,9 @@
       <x:c r="O58" s="2"/>
       <x:c r="P58" s="2"/>
       <x:c r="Q58" s="2"/>
+      <x:c r="R58" s="2"/>
+      <x:c r="S58" s="2"/>
+      <x:c r="T58" s="2"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2"/>
@@ -1990,6 +2318,9 @@
       <x:c r="O59" s="2"/>
       <x:c r="P59" s="2"/>
       <x:c r="Q59" s="2"/>
+      <x:c r="R59" s="2"/>
+      <x:c r="S59" s="2"/>
+      <x:c r="T59" s="2"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2"/>
@@ -2009,6 +2340,9 @@
       <x:c r="O60" s="2"/>
       <x:c r="P60" s="2"/>
       <x:c r="Q60" s="2"/>
+      <x:c r="R60" s="2"/>
+      <x:c r="S60" s="2"/>
+      <x:c r="T60" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2025,12 +2359,15 @@
     <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="72" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="13" customHeight="1">
@@ -2051,6 +2388,9 @@
       <x:c r="O1" s="2"/>
       <x:c r="P1" s="2"/>
       <x:c r="Q1" s="2"/>
+      <x:c r="R1" s="2"/>
+      <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
@@ -2072,6 +2412,9 @@
       <x:c r="O2" s="2"/>
       <x:c r="P2" s="2"/>
       <x:c r="Q2" s="2"/>
+      <x:c r="R2" s="2"/>
+      <x:c r="S2" s="2"/>
+      <x:c r="T2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
@@ -2093,6 +2436,9 @@
       <x:c r="O3" s="2"/>
       <x:c r="P3" s="2"/>
       <x:c r="Q3" s="2"/>
+      <x:c r="R3" s="2"/>
+      <x:c r="S3" s="2"/>
+      <x:c r="T3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -2112,6 +2458,9 @@
       <x:c r="O4" s="2"/>
       <x:c r="P4" s="2"/>
       <x:c r="Q4" s="2"/>
+      <x:c r="R4" s="2"/>
+      <x:c r="S4" s="2"/>
+      <x:c r="T4" s="2"/>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -2141,14 +2490,23 @@
       <x:c r="I5" s="7" t="str">
         <x:v>산정 근거·제약</x:v>
       </x:c>
-      <x:c r="J5" s="2"/>
-      <x:c r="K5" s="2"/>
-      <x:c r="L5" s="2"/>
+      <x:c r="J5" s="7" t="str">
+        <x:v>가정 응답 KB/회</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="str">
+        <x:v>예상 MB/일</x:v>
+      </x:c>
+      <x:c r="L5" s="7" t="str">
+        <x:v>공개 용량 한도</x:v>
+      </x:c>
       <x:c r="M5" s="2"/>
       <x:c r="N5" s="2"/>
       <x:c r="O5" s="2"/>
       <x:c r="P5" s="2"/>
       <x:c r="Q5" s="2"/>
+      <x:c r="R5" s="2"/>
+      <x:c r="S5" s="2"/>
+      <x:c r="T5" s="2"/>
     </x:row>
     <x:row r="6" ht="52" customHeight="1">
       <x:c r="A6" s="8" t="str">
@@ -2157,37 +2515,47 @@
       <x:c r="B6" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="n">
+      <x:c r="C6" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="n">
+      <x:c r="D6" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="n">
+      <x:c r="E6" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="15" t="n">
+      <x:c r="F6" s="19" t="n">
         <x:f>C6*D6*E6</x:f>
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="G6" s="15" t="n">
+      <x:c r="G6" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="str">
+      <x:c r="H6" s="20" t="str">
         <x:f>IF(F6&gt;G6,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
         <x:v>관측소×시간별 갱신. 조위·수온 등 한 응답 공유. 지점 수는 가정.</x:v>
       </x:c>
-      <x:c r="J6" s="2"/>
-      <x:c r="K6" s="2"/>
-      <x:c r="L6" s="2"/>
+      <x:c r="J6" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="n">
+        <x:f>F6*J6/1000</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M6" s="2"/>
       <x:c r="N6" s="2"/>
       <x:c r="O6" s="2"/>
       <x:c r="P6" s="2"/>
       <x:c r="Q6" s="2"/>
+      <x:c r="R6" s="2"/>
+      <x:c r="S6" s="2"/>
+      <x:c r="T6" s="2"/>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
       <x:c r="A7" s="8" t="str">
@@ -2196,37 +2564,47 @@
       <x:c r="B7" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="n">
+      <x:c r="C7" s="18" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F7" s="15" t="n">
+      <x:c r="F7" s="19" t="n">
         <x:f>C7*D7*E7</x:f>
         <x:v>960</x:v>
       </x:c>
-      <x:c r="G7" s="15" t="n">
+      <x:c r="G7" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H7" s="16" t="str">
+      <x:c r="H7" s="20" t="str">
         <x:f>IF(F7&gt;G7,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
         <x:v>부이×시간별 갱신. 수온·유향·유속 한 응답 공유. 지점 수는 가정.</x:v>
       </x:c>
-      <x:c r="J7" s="2"/>
-      <x:c r="K7" s="2"/>
-      <x:c r="L7" s="2"/>
+      <x:c r="J7" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="16" t="n">
+        <x:f>F7*J7/1000</x:f>
+        <x:v>9.6</x:v>
+      </x:c>
+      <x:c r="L7" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M7" s="2"/>
       <x:c r="N7" s="2"/>
       <x:c r="O7" s="2"/>
       <x:c r="P7" s="2"/>
       <x:c r="Q7" s="2"/>
+      <x:c r="R7" s="2"/>
+      <x:c r="S7" s="2"/>
+      <x:c r="T7" s="2"/>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
       <x:c r="A8" s="8" t="str">
@@ -2235,37 +2613,47 @@
       <x:c r="B8" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="n">
+      <x:c r="C8" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="n">
+      <x:c r="D8" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="n">
+      <x:c r="E8" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="n">
+      <x:c r="F8" s="19" t="n">
         <x:f>C8*D8*E8</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="n">
+      <x:c r="G8" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H8" s="16" t="str">
+      <x:c r="H8" s="20" t="str">
         <x:f>IF(F8&gt;G8,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>예보지점×요청일. 만조·간조 시각 이벤트. 지점 수는 가정.</x:v>
       </x:c>
-      <x:c r="J8" s="2"/>
-      <x:c r="K8" s="2"/>
-      <x:c r="L8" s="2"/>
+      <x:c r="J8" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:f>F8*J8/1000</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L8" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M8" s="2"/>
       <x:c r="N8" s="2"/>
       <x:c r="O8" s="2"/>
       <x:c r="P8" s="2"/>
       <x:c r="Q8" s="2"/>
+      <x:c r="R8" s="2"/>
+      <x:c r="S8" s="2"/>
+      <x:c r="T8" s="2"/>
     </x:row>
     <x:row r="9" ht="52" customHeight="1">
       <x:c r="A9" s="8" t="str">
@@ -2274,37 +2662,47 @@
       <x:c r="B9" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="n">
+      <x:c r="C9" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="n">
+      <x:c r="D9" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="n">
+      <x:c r="E9" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="n">
+      <x:c r="F9" s="19" t="n">
         <x:f>C9*D9*E9</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="n">
+      <x:c r="G9" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str">
+      <x:c r="H9" s="20" t="str">
         <x:f>IF(F9&gt;G9,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
         <x:v>예보지점×요청일. 시간 간격을 요청. 지점 수는 가정.</x:v>
       </x:c>
-      <x:c r="J9" s="2"/>
-      <x:c r="K9" s="2"/>
-      <x:c r="L9" s="2"/>
+      <x:c r="J9" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:f>F9*J9/1000</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L9" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M9" s="2"/>
       <x:c r="N9" s="2"/>
       <x:c r="O9" s="2"/>
       <x:c r="P9" s="2"/>
       <x:c r="Q9" s="2"/>
+      <x:c r="R9" s="2"/>
+      <x:c r="S9" s="2"/>
+      <x:c r="T9" s="2"/>
     </x:row>
     <x:row r="10" ht="52" customHeight="1">
       <x:c r="A10" s="8" t="str">
@@ -2313,37 +2711,47 @@
       <x:c r="B10" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="n">
+      <x:c r="C10" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="n">
+      <x:c r="D10" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="n">
+      <x:c r="E10" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="n">
+      <x:c r="F10" s="19" t="n">
         <x:f>C10*D10*E10</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="n">
+      <x:c r="G10" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="str">
+      <x:c r="H10" s="20" t="str">
         <x:f>IF(F10&gt;G10,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
         <x:v>해역 타일×미래 24개 시각 가정. 실제 허용 bbox·페이지·모델 발표주기 미검증.</x:v>
       </x:c>
-      <x:c r="J10" s="2"/>
-      <x:c r="K10" s="2"/>
-      <x:c r="L10" s="2"/>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:f>F10*J10/1000</x:f>
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L10" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M10" s="2"/>
       <x:c r="N10" s="2"/>
       <x:c r="O10" s="2"/>
       <x:c r="P10" s="2"/>
       <x:c r="Q10" s="2"/>
+      <x:c r="R10" s="2"/>
+      <x:c r="S10" s="2"/>
+      <x:c r="T10" s="2"/>
     </x:row>
     <x:row r="11" ht="52" customHeight="1">
       <x:c r="A11" s="8" t="str">
@@ -2352,37 +2760,47 @@
       <x:c r="B11" s="8" t="str">
         <x:v>국립해양조사원</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="n">
+      <x:c r="C11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="n">
+      <x:c r="D11" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="n">
+      <x:c r="E11" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="n">
+      <x:c r="F11" s="19" t="n">
         <x:f>C11*D11*E11</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="n">
+      <x:c r="G11" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H11" s="16" t="str">
+      <x:c r="H11" s="20" t="str">
         <x:f>IF(F11&gt;G11,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
         <x:v>해수욕장×시간별 갱신. 운영 해수욕장 10곳 기준, 계절 운영.</x:v>
       </x:c>
-      <x:c r="J11" s="2"/>
-      <x:c r="K11" s="2"/>
-      <x:c r="L11" s="2"/>
+      <x:c r="J11" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
+        <x:f>F11*J11/1000</x:f>
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="L11" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M11" s="2"/>
       <x:c r="N11" s="2"/>
       <x:c r="O11" s="2"/>
       <x:c r="P11" s="2"/>
       <x:c r="Q11" s="2"/>
+      <x:c r="R11" s="2"/>
+      <x:c r="S11" s="2"/>
+      <x:c r="T11" s="2"/>
     </x:row>
     <x:row r="12" ht="52" customHeight="1">
       <x:c r="A12" s="8" t="str">
@@ -2391,37 +2809,47 @@
       <x:c r="B12" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="n">
+      <x:c r="C12" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="n">
+      <x:c r="D12" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="n">
+      <x:c r="E12" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="n">
+      <x:c r="F12" s="19" t="n">
         <x:f>C12*D12*E12</x:f>
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="n">
+      <x:c r="G12" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="str">
+      <x:c r="H12" s="20" t="str">
         <x:f>IF(F12&gt;G12,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I12" s="8" t="str">
         <x:v>수위관측소×시간별 갱신. 수위·유량 한 응답 공유. 지점 수는 가정.</x:v>
       </x:c>
-      <x:c r="J12" s="2"/>
-      <x:c r="K12" s="2"/>
-      <x:c r="L12" s="2"/>
+      <x:c r="J12" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:f>F12*J12/1000</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L12" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M12" s="2"/>
       <x:c r="N12" s="2"/>
       <x:c r="O12" s="2"/>
       <x:c r="P12" s="2"/>
       <x:c r="Q12" s="2"/>
+      <x:c r="R12" s="2"/>
+      <x:c r="S12" s="2"/>
+      <x:c r="T12" s="2"/>
     </x:row>
     <x:row r="13" ht="52" customHeight="1">
       <x:c r="A13" s="8" t="str">
@@ -2430,37 +2858,47 @@
       <x:c r="B13" s="8" t="str">
         <x:v>한국수자원공사</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="n">
+      <x:c r="C13" s="18" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="n">
+      <x:c r="D13" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="n">
+      <x:c r="E13" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="n">
+      <x:c r="F13" s="19" t="n">
         <x:f>C13*D13*E13</x:f>
         <x:v>1464</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="n">
+      <x:c r="G13" s="19" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str">
+      <x:c r="H13" s="20" t="str">
         <x:f>IF(F13&gt;G13,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I13" s="8" t="str">
         <x:v>댐·보 61지점×시간별 갱신. 수위·유입·방류 한 응답 공유.</x:v>
       </x:c>
-      <x:c r="J13" s="2"/>
-      <x:c r="K13" s="2"/>
-      <x:c r="L13" s="2"/>
+      <x:c r="J13" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
+        <x:f>F13*J13/1000</x:f>
+        <x:v>14.64</x:v>
+      </x:c>
+      <x:c r="L13" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M13" s="2"/>
       <x:c r="N13" s="2"/>
       <x:c r="O13" s="2"/>
       <x:c r="P13" s="2"/>
       <x:c r="Q13" s="2"/>
+      <x:c r="R13" s="2"/>
+      <x:c r="S13" s="2"/>
+      <x:c r="T13" s="2"/>
     </x:row>
     <x:row r="14" ht="52" customHeight="1">
       <x:c r="A14" s="8" t="str">
@@ -2469,37 +2907,47 @@
       <x:c r="B14" s="8" t="str">
         <x:v>기상청 APIHub</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="n">
+      <x:c r="C14" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="n">
+      <x:c r="D14" s="18" t="n">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="n">
+      <x:c r="E14" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="n">
+      <x:c r="F14" s="19" t="n">
         <x:f>C14*D14*E14</x:f>
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="n">
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="H14" s="16" t="str">
+      <x:c r="G14" s="19" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="str">
         <x:f>IF(F14&gt;G14,"초과","건수상 여유")</x:f>
         <x:v>건수상 여유</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
         <x:v>전국 좌표 원시자료 10분마다 1회. 시간 중복 제거 후 nx/ny에 배정. 응답 바이트 미측정.</x:v>
       </x:c>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
-      <x:c r="L14" s="2"/>
+      <x:c r="J14" s="15" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:f>F14*J14/1000</x:f>
+        <x:v>14.4</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="str">
+        <x:v>일반회원 공식 5GB/일</x:v>
+      </x:c>
       <x:c r="M14" s="2"/>
       <x:c r="N14" s="2"/>
       <x:c r="O14" s="2"/>
       <x:c r="P14" s="2"/>
       <x:c r="Q14" s="2"/>
+      <x:c r="R14" s="2"/>
+      <x:c r="S14" s="2"/>
+      <x:c r="T14" s="2"/>
     </x:row>
     <x:row r="15" ht="52" customHeight="1">
       <x:c r="A15" s="8" t="str">
@@ -2508,35 +2956,45 @@
       <x:c r="B15" s="8" t="str">
         <x:v>국립수산과학원</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="n">
+      <x:c r="C15" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="14" t="n">
+      <x:c r="D15" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="n">
+      <x:c r="E15" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="n">
+      <x:c r="F15" s="19" t="n">
         <x:f>C15*D15*E15</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G15" s="15"/>
-      <x:c r="H15" s="16" t="str">
+      <x:c r="G15" s="19"/>
+      <x:c r="H15" s="20" t="str">
         <x:f>"계정 한도 미확인"</x:f>
         <x:v>계정 한도 미확인</x:v>
       </x:c>
       <x:c r="I15" s="8" t="str">
         <x:v>하루 4회 목록 확인 가정. 새 속보/주간보고 상세는 건별 추가. 시간별 격자 지수 아님.</x:v>
       </x:c>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
-      <x:c r="L15" s="2"/>
+      <x:c r="J15" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:f>F15*J15/1000</x:f>
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="str">
+        <x:v>공개 명세에서 확인 못함</x:v>
+      </x:c>
       <x:c r="M15" s="2"/>
       <x:c r="N15" s="2"/>
       <x:c r="O15" s="2"/>
       <x:c r="P15" s="2"/>
       <x:c r="Q15" s="2"/>
+      <x:c r="R15" s="2"/>
+      <x:c r="S15" s="2"/>
+      <x:c r="T15" s="2"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2"/>
@@ -2556,6 +3014,9 @@
       <x:c r="O16" s="2"/>
       <x:c r="P16" s="2"/>
       <x:c r="Q16" s="2"/>
+      <x:c r="R16" s="2"/>
+      <x:c r="S16" s="2"/>
+      <x:c r="T16" s="2"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2"/>
@@ -2575,6 +3036,9 @@
       <x:c r="O17" s="2"/>
       <x:c r="P17" s="2"/>
       <x:c r="Q17" s="2"/>
+      <x:c r="R17" s="2"/>
+      <x:c r="S17" s="2"/>
+      <x:c r="T17" s="2"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="str">
@@ -2583,7 +3047,9 @@
       <x:c r="B18" s="2" t="str">
         <x:v>예상 중복 제거 호출/일</x:v>
       </x:c>
-      <x:c r="C18" s="2"/>
+      <x:c r="C18" s="2" t="str">
+        <x:v>가정 응답 용량 MB/일</x:v>
+      </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2"/>
@@ -2598,6 +3064,9 @@
       <x:c r="O18" s="2"/>
       <x:c r="P18" s="2"/>
       <x:c r="Q18" s="2"/>
+      <x:c r="R18" s="2"/>
+      <x:c r="S18" s="2"/>
+      <x:c r="T18" s="2"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="str">
@@ -2607,7 +3076,10 @@
         <x:f>SUMIFS(F6:F15,B6:B15,A19)</x:f>
         <x:v>2740</x:v>
       </x:c>
-      <x:c r="C19" s="2"/>
+      <x:c r="C19" s="2" t="n">
+        <x:f>SUMIFS(K6:K15,B6:B15,A19)</x:f>
+        <x:v>265</x:v>
+      </x:c>
       <x:c r="D19" s="2"/>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2"/>
@@ -2622,6 +3094,9 @@
       <x:c r="O19" s="2"/>
       <x:c r="P19" s="2"/>
       <x:c r="Q19" s="2"/>
+      <x:c r="R19" s="2"/>
+      <x:c r="S19" s="2"/>
+      <x:c r="T19" s="2"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="str">
@@ -2631,7 +3106,10 @@
         <x:f>SUMIFS(F6:F15,B6:B15,A20)</x:f>
         <x:v>3864</x:v>
       </x:c>
-      <x:c r="C20" s="2"/>
+      <x:c r="C20" s="2" t="n">
+        <x:f>SUMIFS(K6:K15,B6:B15,A20)</x:f>
+        <x:v>38.64</x:v>
+      </x:c>
       <x:c r="D20" s="2"/>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2"/>
@@ -2646,6 +3124,9 @@
       <x:c r="O20" s="2"/>
       <x:c r="P20" s="2"/>
       <x:c r="Q20" s="2"/>
+      <x:c r="R20" s="2"/>
+      <x:c r="S20" s="2"/>
+      <x:c r="T20" s="2"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="str">
@@ -2655,7 +3136,10 @@
         <x:f>SUMIFS(F6:F15,B6:B15,A21)</x:f>
         <x:v>144</x:v>
       </x:c>
-      <x:c r="C21" s="2"/>
+      <x:c r="C21" s="2" t="n">
+        <x:f>SUMIFS(K6:K15,B6:B15,A21)</x:f>
+        <x:v>14.4</x:v>
+      </x:c>
       <x:c r="D21" s="2"/>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2"/>
@@ -2670,6 +3154,9 @@
       <x:c r="O21" s="2"/>
       <x:c r="P21" s="2"/>
       <x:c r="Q21" s="2"/>
+      <x:c r="R21" s="2"/>
+      <x:c r="S21" s="2"/>
+      <x:c r="T21" s="2"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2"/>
@@ -2689,6 +3176,9 @@
       <x:c r="O22" s="2"/>
       <x:c r="P22" s="2"/>
       <x:c r="Q22" s="2"/>
+      <x:c r="R22" s="2"/>
+      <x:c r="S22" s="2"/>
+      <x:c r="T22" s="2"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="str">
@@ -2712,6 +3202,9 @@
       <x:c r="O23" s="2"/>
       <x:c r="P23" s="2"/>
       <x:c r="Q23" s="2"/>
+      <x:c r="R23" s="2"/>
+      <x:c r="S23" s="2"/>
+      <x:c r="T23" s="2"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="str">
@@ -2735,6 +3228,9 @@
       <x:c r="O24" s="2"/>
       <x:c r="P24" s="2"/>
       <x:c r="Q24" s="2"/>
+      <x:c r="R24" s="2"/>
+      <x:c r="S24" s="2"/>
+      <x:c r="T24" s="2"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2"/>
@@ -2754,6 +3250,9 @@
       <x:c r="O25" s="2"/>
       <x:c r="P25" s="2"/>
       <x:c r="Q25" s="2"/>
+      <x:c r="R25" s="2"/>
+      <x:c r="S25" s="2"/>
+      <x:c r="T25" s="2"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="2"/>
@@ -2773,10 +3272,17 @@
       <x:c r="O26" s="2"/>
       <x:c r="P26" s="2"/>
       <x:c r="Q26" s="2"/>
+      <x:c r="R26" s="2"/>
+      <x:c r="S26" s="2"/>
+      <x:c r="T26" s="2"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="2"/>
-      <x:c r="B27" s="2"/>
+      <x:c r="A27" s="2" t="str">
+        <x:v>APIHub 공식 5GB 용량 판정</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>단위 MB(10진). 기존 필수 3,842MB + 재시도 최대 예약 400MB = 4,242MB. 서버 내부 보호선은 판정 기준에서 제외한다.</x:v>
+      </x:c>
       <x:c r="C27" s="2"/>
       <x:c r="D27" s="2"/>
       <x:c r="E27" s="2"/>
@@ -2792,6 +3298,9 @@
       <x:c r="O27" s="2"/>
       <x:c r="P27" s="2"/>
       <x:c r="Q27" s="2"/>
+      <x:c r="R27" s="2"/>
+      <x:c r="S27" s="2"/>
+      <x:c r="T27" s="2"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2"/>
@@ -2811,15 +3320,30 @@
       <x:c r="O28" s="2"/>
       <x:c r="P28" s="2"/>
       <x:c r="Q28" s="2"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="2"/>
-      <x:c r="B29" s="2"/>
+      <x:c r="R28" s="2"/>
+      <x:c r="S28" s="2"/>
+      <x:c r="T28" s="2"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="2" t="str">
+        <x:v>공식 1일 용량 MB</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
       <x:c r="C29" s="2"/>
-      <x:c r="D29" s="2"/>
-      <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
+      <x:c r="D29" s="8" t="str">
+        <x:v>낙뢰 응답 가정 MB/회</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="str">
+        <x:v>하루 낙뢰 용량 MB</x:v>
+      </x:c>
+      <x:c r="F29" s="8" t="str">
+        <x:v>기존 겨울 예산 합산 MB</x:v>
+      </x:c>
+      <x:c r="G29" s="8" t="str">
+        <x:v>공식 5GB 판정</x:v>
+      </x:c>
       <x:c r="H29" s="2"/>
       <x:c r="I29" s="2"/>
       <x:c r="J29" s="2"/>
@@ -2830,15 +3354,33 @@
       <x:c r="O29" s="2"/>
       <x:c r="P29" s="2"/>
       <x:c r="Q29" s="2"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="2"/>
-      <x:c r="B30" s="2"/>
+      <x:c r="R29" s="2"/>
+      <x:c r="S29" s="2"/>
+      <x:c r="T29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="2" t="str">
+        <x:v>공식 1일 호출 한도</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="n">
+        <x:v>20000</x:v>
+      </x:c>
       <x:c r="C30" s="2"/>
-      <x:c r="D30" s="2"/>
-      <x:c r="E30" s="2"/>
-      <x:c r="F30" s="2"/>
-      <x:c r="G30" s="2"/>
+      <x:c r="D30" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="n">
+        <x:f>D30*$B$32</x:f>
+        <x:v>14.4</x:v>
+      </x:c>
+      <x:c r="F30" s="8" t="n">
+        <x:f>$B$31+E30</x:f>
+        <x:v>4256.4</x:v>
+      </x:c>
+      <x:c r="G30" s="8" t="str">
+        <x:f>IF(F30&lt;=$B$29,"가능","불가능")</x:f>
+        <x:v>가능</x:v>
+      </x:c>
       <x:c r="H30" s="2"/>
       <x:c r="I30" s="2"/>
       <x:c r="J30" s="2"/>
@@ -2849,15 +3391,33 @@
       <x:c r="O30" s="2"/>
       <x:c r="P30" s="2"/>
       <x:c r="Q30" s="2"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="2"/>
-      <x:c r="B31" s="2"/>
+      <x:c r="R30" s="2"/>
+      <x:c r="S30" s="2"/>
+      <x:c r="T30" s="2"/>
+    </x:row>
+    <x:row r="31" ht="38" customHeight="1">
+      <x:c r="A31" s="2" t="str">
+        <x:v>기존 겨울 예산 MB</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="n">
+        <x:v>4242</x:v>
+      </x:c>
       <x:c r="C31" s="2"/>
-      <x:c r="D31" s="2"/>
-      <x:c r="E31" s="2"/>
-      <x:c r="F31" s="2"/>
-      <x:c r="G31" s="2"/>
+      <x:c r="D31" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="n">
+        <x:f>D31*$B$32</x:f>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="n">
+        <x:f>$B$31+E31</x:f>
+        <x:v>4386</x:v>
+      </x:c>
+      <x:c r="G31" s="8" t="str">
+        <x:f>IF(F31&lt;=$B$29,"가능","불가능")</x:f>
+        <x:v>가능</x:v>
+      </x:c>
       <x:c r="H31" s="2"/>
       <x:c r="I31" s="2"/>
       <x:c r="J31" s="2"/>
@@ -2868,15 +3428,34 @@
       <x:c r="O31" s="2"/>
       <x:c r="P31" s="2"/>
       <x:c r="Q31" s="2"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="2"/>
-      <x:c r="B32" s="2"/>
+      <x:c r="R31" s="2"/>
+      <x:c r="S31" s="2"/>
+      <x:c r="T31" s="2"/>
+    </x:row>
+    <x:row r="32" ht="38" customHeight="1">
+      <x:c r="A32" s="2" t="str">
+        <x:v>낙뢰 조회/일</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="n">
+        <x:f>F14</x:f>
+        <x:v>144</x:v>
+      </x:c>
       <x:c r="C32" s="2"/>
-      <x:c r="D32" s="2"/>
-      <x:c r="E32" s="2"/>
-      <x:c r="F32" s="2"/>
-      <x:c r="G32" s="2"/>
+      <x:c r="D32" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" s="8" t="n">
+        <x:f>D32*$B$32</x:f>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="n">
+        <x:f>$B$31+E32</x:f>
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="str">
+        <x:f>IF(F32&lt;=$B$29,"가능","불가능")</x:f>
+        <x:v>가능</x:v>
+      </x:c>
       <x:c r="H32" s="2"/>
       <x:c r="I32" s="2"/>
       <x:c r="J32" s="2"/>
@@ -2887,15 +3466,31 @@
       <x:c r="O32" s="2"/>
       <x:c r="P32" s="2"/>
       <x:c r="Q32" s="2"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="2"/>
-      <x:c r="B33" s="2"/>
+      <x:c r="R32" s="2"/>
+      <x:c r="S32" s="2"/>
+      <x:c r="T32" s="2"/>
+    </x:row>
+    <x:row r="33" ht="38" customHeight="1">
+      <x:c r="A33" s="2" t="str">
+        <x:v>공식 한도 허용 평균 MB/회</x:v>
+      </x:c>
+      <x:c r="B33" s="17" t="n">
+        <x:f>(B29-B31)/B32</x:f>
+        <x:v>5.263888888888889</x:v>
+      </x:c>
       <x:c r="C33" s="2"/>
-      <x:c r="D33" s="2"/>
-      <x:c r="E33" s="2"/>
-      <x:c r="F33" s="2"/>
-      <x:c r="G33" s="2"/>
+      <x:c r="D33" s="8" t="str">
+        <x:v>판정 기준</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="str">
+        <x:v>상한 약 5.264MB/회</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>실제 바이트·당일 사용량 미확인</x:v>
+      </x:c>
+      <x:c r="G33" s="8" t="str">
+        <x:v>기존 계획값 기준</x:v>
+      </x:c>
       <x:c r="H33" s="2"/>
       <x:c r="I33" s="2"/>
       <x:c r="J33" s="2"/>
@@ -2906,10 +3501,18 @@
       <x:c r="O33" s="2"/>
       <x:c r="P33" s="2"/>
       <x:c r="Q33" s="2"/>
+      <x:c r="R33" s="2"/>
+      <x:c r="S33" s="2"/>
+      <x:c r="T33" s="2"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="2"/>
-      <x:c r="B34" s="2"/>
+      <x:c r="A34" s="2" t="str">
+        <x:v>낙뢰 가정 응답 MB/일</x:v>
+      </x:c>
+      <x:c r="B34" s="17" t="n">
+        <x:f>K14</x:f>
+        <x:v>14.4</x:v>
+      </x:c>
       <x:c r="C34" s="2"/>
       <x:c r="D34" s="2"/>
       <x:c r="E34" s="2"/>
@@ -2925,10 +3528,18 @@
       <x:c r="O34" s="2"/>
       <x:c r="P34" s="2"/>
       <x:c r="Q34" s="2"/>
+      <x:c r="R34" s="2"/>
+      <x:c r="S34" s="2"/>
+      <x:c r="T34" s="2"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
+      <x:c r="A35" s="2" t="str">
+        <x:v>가정 응답 반영 후 공식 잔여 MB</x:v>
+      </x:c>
+      <x:c r="B35" s="17" t="n">
+        <x:f>B29-B31-B34</x:f>
+        <x:v>743.6</x:v>
+      </x:c>
       <x:c r="C35" s="2"/>
       <x:c r="D35" s="2"/>
       <x:c r="E35" s="2"/>
@@ -2944,6 +3555,9 @@
       <x:c r="O35" s="2"/>
       <x:c r="P35" s="2"/>
       <x:c r="Q35" s="2"/>
+      <x:c r="R35" s="2"/>
+      <x:c r="S35" s="2"/>
+      <x:c r="T35" s="2"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2"/>
@@ -2963,6 +3577,9 @@
       <x:c r="O36" s="2"/>
       <x:c r="P36" s="2"/>
       <x:c r="Q36" s="2"/>
+      <x:c r="R36" s="2"/>
+      <x:c r="S36" s="2"/>
+      <x:c r="T36" s="2"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2"/>
@@ -2982,6 +3599,9 @@
       <x:c r="O37" s="2"/>
       <x:c r="P37" s="2"/>
       <x:c r="Q37" s="2"/>
+      <x:c r="R37" s="2"/>
+      <x:c r="S37" s="2"/>
+      <x:c r="T37" s="2"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2"/>
@@ -3001,10 +3621,17 @@
       <x:c r="O38" s="2"/>
       <x:c r="P38" s="2"/>
       <x:c r="Q38" s="2"/>
+      <x:c r="R38" s="2"/>
+      <x:c r="S38" s="2"/>
+      <x:c r="T38" s="2"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="2"/>
-      <x:c r="B39" s="2"/>
+      <x:c r="A39" s="2" t="str">
+        <x:v>하천 10분 운영안</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="str">
+        <x:v>일일 호출</x:v>
+      </x:c>
       <x:c r="C39" s="2"/>
       <x:c r="D39" s="2"/>
       <x:c r="E39" s="2"/>
@@ -3020,10 +3647,18 @@
       <x:c r="O39" s="2"/>
       <x:c r="P39" s="2"/>
       <x:c r="Q39" s="2"/>
+      <x:c r="R39" s="2"/>
+      <x:c r="S39" s="2"/>
+      <x:c r="T39" s="2"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
+      <x:c r="A40" s="2" t="str">
+        <x:v>개발계정 안내 한도</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="n">
+        <x:f>G12</x:f>
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="C40" s="2"/>
       <x:c r="D40" s="2"/>
       <x:c r="E40" s="2"/>
@@ -3039,10 +3674,18 @@
       <x:c r="O40" s="2"/>
       <x:c r="P40" s="2"/>
       <x:c r="Q40" s="2"/>
+      <x:c r="R40" s="2"/>
+      <x:c r="S40" s="2"/>
+      <x:c r="T40" s="2"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
+      <x:c r="A41" s="2" t="str">
+        <x:v>10분 수집 필요 호출</x:v>
+      </x:c>
+      <x:c r="B41" s="2" t="n">
+        <x:f>C12*144</x:f>
+        <x:v>14400</x:v>
+      </x:c>
       <x:c r="C41" s="2"/>
       <x:c r="D41" s="2"/>
       <x:c r="E41" s="2"/>
@@ -3058,10 +3701,18 @@
       <x:c r="O41" s="2"/>
       <x:c r="P41" s="2"/>
       <x:c r="Q41" s="2"/>
+      <x:c r="R41" s="2"/>
+      <x:c r="S41" s="2"/>
+      <x:c r="T41" s="2"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
+      <x:c r="A42" s="2" t="str">
+        <x:v>개발계정 부족분</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="n">
+        <x:f>B41-B40</x:f>
+        <x:v>4400</x:v>
+      </x:c>
       <x:c r="C42" s="2"/>
       <x:c r="D42" s="2"/>
       <x:c r="E42" s="2"/>
@@ -3077,10 +3728,18 @@
       <x:c r="O42" s="2"/>
       <x:c r="P42" s="2"/>
       <x:c r="Q42" s="2"/>
+      <x:c r="R42" s="2"/>
+      <x:c r="S42" s="2"/>
+      <x:c r="T42" s="2"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
+      <x:c r="A43" s="2" t="str">
+        <x:v>운영계정 신청 최소</x:v>
+      </x:c>
+      <x:c r="B43" s="2" t="n">
+        <x:f>B41</x:f>
+        <x:v>14400</x:v>
+      </x:c>
       <x:c r="C43" s="2"/>
       <x:c r="D43" s="2"/>
       <x:c r="E43" s="2"/>
@@ -3096,9 +3755,14 @@
       <x:c r="O43" s="2"/>
       <x:c r="P43" s="2"/>
       <x:c r="Q43" s="2"/>
+      <x:c r="R43" s="2"/>
+      <x:c r="S43" s="2"/>
+      <x:c r="T43" s="2"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="2"/>
+      <x:c r="A44" s="2" t="str">
+        <x:v>운영계정 한도 상향 가능. 고정 횟수 미공개; 승인값 확인 필요.</x:v>
+      </x:c>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
       <x:c r="D44" s="2"/>
@@ -3115,6 +3779,9 @@
       <x:c r="O44" s="2"/>
       <x:c r="P44" s="2"/>
       <x:c r="Q44" s="2"/>
+      <x:c r="R44" s="2"/>
+      <x:c r="S44" s="2"/>
+      <x:c r="T44" s="2"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2"/>
@@ -3134,10 +3801,17 @@
       <x:c r="O45" s="2"/>
       <x:c r="P45" s="2"/>
       <x:c r="Q45" s="2"/>
+      <x:c r="R45" s="2"/>
+      <x:c r="S45" s="2"/>
+      <x:c r="T45" s="2"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="2"/>
-      <x:c r="B46" s="2"/>
+      <x:c r="A46" s="2" t="str">
+        <x:v>운영계정 공개 고정 한도</x:v>
+      </x:c>
+      <x:c r="B46" s="2" t="str">
+        <x:v>숫자 미공개; 활용사례 등록 후 증량 신청</x:v>
+      </x:c>
       <x:c r="C46" s="2"/>
       <x:c r="D46" s="2"/>
       <x:c r="E46" s="2"/>
@@ -3153,10 +3827,15 @@
       <x:c r="O46" s="2"/>
       <x:c r="P46" s="2"/>
       <x:c r="Q46" s="2"/>
+      <x:c r="R46" s="2"/>
+      <x:c r="S46" s="2"/>
+      <x:c r="T46" s="2"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="2"/>
-      <x:c r="B47" s="2"/>
+      <x:c r="A47" s="2" t="str">
+        <x:v>실제 승인 일한도(사용자 입력)</x:v>
+      </x:c>
+      <x:c r="B47" s="12"/>
       <x:c r="C47" s="2"/>
       <x:c r="D47" s="2"/>
       <x:c r="E47" s="2"/>
@@ -3172,10 +3851,18 @@
       <x:c r="O47" s="2"/>
       <x:c r="P47" s="2"/>
       <x:c r="Q47" s="2"/>
+      <x:c r="R47" s="2"/>
+      <x:c r="S47" s="2"/>
+      <x:c r="T47" s="2"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="2"/>
-      <x:c r="B48" s="2"/>
+      <x:c r="A48" s="2" t="str">
+        <x:v>승인량 기준 10분안 결과</x:v>
+      </x:c>
+      <x:c r="B48" s="2" t="str">
+        <x:f>IF(B47="","승인량 미확인",IF(B47&gt;=B41,"가능","부족"))</x:f>
+        <x:v>승인량 미확인</x:v>
+      </x:c>
       <x:c r="C48" s="2"/>
       <x:c r="D48" s="2"/>
       <x:c r="E48" s="2"/>
@@ -3191,6 +3878,9 @@
       <x:c r="O48" s="2"/>
       <x:c r="P48" s="2"/>
       <x:c r="Q48" s="2"/>
+      <x:c r="R48" s="2"/>
+      <x:c r="S48" s="2"/>
+      <x:c r="T48" s="2"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2"/>
@@ -3210,6 +3900,9 @@
       <x:c r="O49" s="2"/>
       <x:c r="P49" s="2"/>
       <x:c r="Q49" s="2"/>
+      <x:c r="R49" s="2"/>
+      <x:c r="S49" s="2"/>
+      <x:c r="T49" s="2"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2"/>
@@ -3229,6 +3922,9 @@
       <x:c r="O50" s="2"/>
       <x:c r="P50" s="2"/>
       <x:c r="Q50" s="2"/>
+      <x:c r="R50" s="2"/>
+      <x:c r="S50" s="2"/>
+      <x:c r="T50" s="2"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2"/>
@@ -3248,6 +3944,9 @@
       <x:c r="O51" s="2"/>
       <x:c r="P51" s="2"/>
       <x:c r="Q51" s="2"/>
+      <x:c r="R51" s="2"/>
+      <x:c r="S51" s="2"/>
+      <x:c r="T51" s="2"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2"/>
@@ -3267,6 +3966,9 @@
       <x:c r="O52" s="2"/>
       <x:c r="P52" s="2"/>
       <x:c r="Q52" s="2"/>
+      <x:c r="R52" s="2"/>
+      <x:c r="S52" s="2"/>
+      <x:c r="T52" s="2"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2"/>
@@ -3286,6 +3988,9 @@
       <x:c r="O53" s="2"/>
       <x:c r="P53" s="2"/>
       <x:c r="Q53" s="2"/>
+      <x:c r="R53" s="2"/>
+      <x:c r="S53" s="2"/>
+      <x:c r="T53" s="2"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2"/>
@@ -3305,6 +4010,9 @@
       <x:c r="O54" s="2"/>
       <x:c r="P54" s="2"/>
       <x:c r="Q54" s="2"/>
+      <x:c r="R54" s="2"/>
+      <x:c r="S54" s="2"/>
+      <x:c r="T54" s="2"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2"/>
@@ -3324,6 +4032,9 @@
       <x:c r="O55" s="2"/>
       <x:c r="P55" s="2"/>
       <x:c r="Q55" s="2"/>
+      <x:c r="R55" s="2"/>
+      <x:c r="S55" s="2"/>
+      <x:c r="T55" s="2"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2"/>
@@ -3343,6 +4054,9 @@
       <x:c r="O56" s="2"/>
       <x:c r="P56" s="2"/>
       <x:c r="Q56" s="2"/>
+      <x:c r="R56" s="2"/>
+      <x:c r="S56" s="2"/>
+      <x:c r="T56" s="2"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2"/>
@@ -3362,6 +4076,9 @@
       <x:c r="O57" s="2"/>
       <x:c r="P57" s="2"/>
       <x:c r="Q57" s="2"/>
+      <x:c r="R57" s="2"/>
+      <x:c r="S57" s="2"/>
+      <x:c r="T57" s="2"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2"/>
@@ -3381,6 +4098,9 @@
       <x:c r="O58" s="2"/>
       <x:c r="P58" s="2"/>
       <x:c r="Q58" s="2"/>
+      <x:c r="R58" s="2"/>
+      <x:c r="S58" s="2"/>
+      <x:c r="T58" s="2"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2"/>
@@ -3400,6 +4120,9 @@
       <x:c r="O59" s="2"/>
       <x:c r="P59" s="2"/>
       <x:c r="Q59" s="2"/>
+      <x:c r="R59" s="2"/>
+      <x:c r="S59" s="2"/>
+      <x:c r="T59" s="2"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2"/>
@@ -3419,6 +4142,9 @@
       <x:c r="O60" s="2"/>
       <x:c r="P60" s="2"/>
       <x:c r="Q60" s="2"/>
+      <x:c r="R60" s="2"/>
+      <x:c r="S60" s="2"/>
+      <x:c r="T60" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3453,6 +4179,9 @@
       <x:c r="O1" s="2"/>
       <x:c r="P1" s="2"/>
       <x:c r="Q1" s="2"/>
+      <x:c r="R1" s="2"/>
+      <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
@@ -3474,6 +4203,9 @@
       <x:c r="O2" s="2"/>
       <x:c r="P2" s="2"/>
       <x:c r="Q2" s="2"/>
+      <x:c r="R2" s="2"/>
+      <x:c r="S2" s="2"/>
+      <x:c r="T2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2"/>
@@ -3493,6 +4225,9 @@
       <x:c r="O3" s="2"/>
       <x:c r="P3" s="2"/>
       <x:c r="Q3" s="2"/>
+      <x:c r="R3" s="2"/>
+      <x:c r="S3" s="2"/>
+      <x:c r="T3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
@@ -3516,8 +4251,11 @@
       <x:c r="O4" s="2"/>
       <x:c r="P4" s="2"/>
       <x:c r="Q4" s="2"/>
-    </x:row>
-    <x:row r="5" ht="49" customHeight="1">
+      <x:c r="R4" s="2"/>
+      <x:c r="S4" s="2"/>
+      <x:c r="T4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="55" customHeight="1">
       <x:c r="A5" s="8" t="str">
         <x:v>격자 기준</x:v>
       </x:c>
@@ -3539,8 +4277,11 @@
       <x:c r="O5" s="2"/>
       <x:c r="P5" s="2"/>
       <x:c r="Q5" s="2"/>
-    </x:row>
-    <x:row r="6" ht="49" customHeight="1">
+      <x:c r="R5" s="2"/>
+      <x:c r="S5" s="2"/>
+      <x:c r="T5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="55" customHeight="1">
       <x:c r="A6" s="8" t="str">
         <x:v>표시 원칙</x:v>
       </x:c>
@@ -3562,8 +4303,11 @@
       <x:c r="O6" s="2"/>
       <x:c r="P6" s="2"/>
       <x:c r="Q6" s="2"/>
-    </x:row>
-    <x:row r="7" ht="49" customHeight="1">
+      <x:c r="R6" s="2"/>
+      <x:c r="S6" s="2"/>
+      <x:c r="T6" s="2"/>
+    </x:row>
+    <x:row r="7" ht="55" customHeight="1">
       <x:c r="A7" s="8" t="str">
         <x:v>관측 호출</x:v>
       </x:c>
@@ -3585,8 +4329,11 @@
       <x:c r="O7" s="2"/>
       <x:c r="P7" s="2"/>
       <x:c r="Q7" s="2"/>
-    </x:row>
-    <x:row r="8" ht="49" customHeight="1">
+      <x:c r="R7" s="2"/>
+      <x:c r="S7" s="2"/>
+      <x:c r="T7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="55" customHeight="1">
       <x:c r="A8" s="8" t="str">
         <x:v>예보 호출</x:v>
       </x:c>
@@ -3608,8 +4355,11 @@
       <x:c r="O8" s="2"/>
       <x:c r="P8" s="2"/>
       <x:c r="Q8" s="2"/>
-    </x:row>
-    <x:row r="9" ht="49" customHeight="1">
+      <x:c r="R8" s="2"/>
+      <x:c r="S8" s="2"/>
+      <x:c r="T8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="55" customHeight="1">
       <x:c r="A9" s="8" t="str">
         <x:v>예시 대상</x:v>
       </x:c>
@@ -3631,13 +4381,16 @@
       <x:c r="O9" s="2"/>
       <x:c r="P9" s="2"/>
       <x:c r="Q9" s="2"/>
-    </x:row>
-    <x:row r="10" ht="49" customHeight="1">
+      <x:c r="R9" s="2"/>
+      <x:c r="S9" s="2"/>
+      <x:c r="T9" s="2"/>
+    </x:row>
+    <x:row r="10" ht="55" customHeight="1">
       <x:c r="A10" s="8" t="str">
         <x:v>한도</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>공공데이터포털 각 명세의 개발계정 10,000회/일 안내를 사용. 운영계정 실제 할당량은 조회하지 못했다. APIHub 일반회원 20,000회·5GB, 서버 내부 18,000회·4.5GB.</x:v>
+        <x:v>공공데이터포털 해당 API 개발계정은 10,000회/일. 운영계정은 활용사례 등록 후 트래픽 증가 신청 가능하나 고정 적용 수치가 공개되지 않았다. APIHub 일반회원 공식 한도는 20,000회·5GB/일이며 내부 보호선은 이번 판정에서 제외한다.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -3654,8 +4407,11 @@
       <x:c r="O10" s="2"/>
       <x:c r="P10" s="2"/>
       <x:c r="Q10" s="2"/>
-    </x:row>
-    <x:row r="11" ht="49" customHeight="1">
+      <x:c r="R10" s="2"/>
+      <x:c r="S10" s="2"/>
+      <x:c r="T10" s="2"/>
+    </x:row>
+    <x:row r="11" ht="55" customHeight="1">
       <x:c r="A11" s="8" t="str">
         <x:v>낙뢰</x:v>
       </x:c>
@@ -3677,8 +4433,11 @@
       <x:c r="O11" s="2"/>
       <x:c r="P11" s="2"/>
       <x:c r="Q11" s="2"/>
-    </x:row>
-    <x:row r="12" ht="49" customHeight="1">
+      <x:c r="R11" s="2"/>
+      <x:c r="S11" s="2"/>
+      <x:c r="T11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="55" customHeight="1">
       <x:c r="A12" s="8" t="str">
         <x:v>공유 호출</x:v>
       </x:c>
@@ -3700,8 +4459,11 @@
       <x:c r="O12" s="2"/>
       <x:c r="P12" s="2"/>
       <x:c r="Q12" s="2"/>
-    </x:row>
-    <x:row r="13" ht="49" customHeight="1">
+      <x:c r="R12" s="2"/>
+      <x:c r="S12" s="2"/>
+      <x:c r="T12" s="2"/>
+    </x:row>
+    <x:row r="13" ht="55" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>제외 범위</x:v>
       </x:c>
@@ -3723,10 +4485,17 @@
       <x:c r="O13" s="2"/>
       <x:c r="P13" s="2"/>
       <x:c r="Q13" s="2"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
+      <x:c r="R13" s="2"/>
+      <x:c r="S13" s="2"/>
+      <x:c r="T13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="55" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>APIHub 공식 용량 여유</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>기존 저장소 겨울 계획치 3,842MB+재시도 예약 400MB=4,242MB. 공식 5,000MB까지 758MB 남음. 낙뢰 144회면 허용 평균 758/144=5.264MB/회. 2MB/회 가정 시 합산 4,530MB로 공식 한도 내. 실제 바이트·당일 사용량은 미측정.</x:v>
+      </x:c>
       <x:c r="C14" s="2"/>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2"/>
@@ -3742,10 +4511,17 @@
       <x:c r="O14" s="2"/>
       <x:c r="P14" s="2"/>
       <x:c r="Q14" s="2"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="2"/>
-      <x:c r="B15" s="2"/>
+      <x:c r="R14" s="2"/>
+      <x:c r="S14" s="2"/>
+      <x:c r="T14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="55" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>응답 용량 시나리오</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>API 호출 산정 J열은 실측값이 아닌 편집 가능한 가정: 지점·목록 10KB/회, ROMS 1,000KB/회, 낙뢰 100KB/회. 포털 API는 명세에 바이트 한도가 없어 예상 네트워크량만 계산.</x:v>
+      </x:c>
       <x:c r="C15" s="2"/>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2"/>
@@ -3761,6 +4537,9 @@
       <x:c r="O15" s="2"/>
       <x:c r="P15" s="2"/>
       <x:c r="Q15" s="2"/>
+      <x:c r="R15" s="2"/>
+      <x:c r="S15" s="2"/>
+      <x:c r="T15" s="2"/>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="7" t="str">
@@ -3788,6 +4567,9 @@
       <x:c r="O16" s="2"/>
       <x:c r="P16" s="2"/>
       <x:c r="Q16" s="2"/>
+      <x:c r="R16" s="2"/>
+      <x:c r="S16" s="2"/>
+      <x:c r="T16" s="2"/>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="8" t="str">
@@ -3815,6 +4597,9 @@
       <x:c r="O17" s="2"/>
       <x:c r="P17" s="2"/>
       <x:c r="Q17" s="2"/>
+      <x:c r="R17" s="2"/>
+      <x:c r="S17" s="2"/>
+      <x:c r="T17" s="2"/>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="8" t="str">
@@ -3842,6 +4627,9 @@
       <x:c r="O18" s="2"/>
       <x:c r="P18" s="2"/>
       <x:c r="Q18" s="2"/>
+      <x:c r="R18" s="2"/>
+      <x:c r="S18" s="2"/>
+      <x:c r="T18" s="2"/>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="8" t="str">
@@ -3869,6 +4657,9 @@
       <x:c r="O19" s="2"/>
       <x:c r="P19" s="2"/>
       <x:c r="Q19" s="2"/>
+      <x:c r="R19" s="2"/>
+      <x:c r="S19" s="2"/>
+      <x:c r="T19" s="2"/>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="8" t="str">
@@ -3896,6 +4687,9 @@
       <x:c r="O20" s="2"/>
       <x:c r="P20" s="2"/>
       <x:c r="Q20" s="2"/>
+      <x:c r="R20" s="2"/>
+      <x:c r="S20" s="2"/>
+      <x:c r="T20" s="2"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="8" t="str">
@@ -3923,6 +4717,9 @@
       <x:c r="O21" s="2"/>
       <x:c r="P21" s="2"/>
       <x:c r="Q21" s="2"/>
+      <x:c r="R21" s="2"/>
+      <x:c r="S21" s="2"/>
+      <x:c r="T21" s="2"/>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="8" t="str">
@@ -3950,6 +4747,9 @@
       <x:c r="O22" s="2"/>
       <x:c r="P22" s="2"/>
       <x:c r="Q22" s="2"/>
+      <x:c r="R22" s="2"/>
+      <x:c r="S22" s="2"/>
+      <x:c r="T22" s="2"/>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="8" t="str">
@@ -3977,6 +4777,9 @@
       <x:c r="O23" s="2"/>
       <x:c r="P23" s="2"/>
       <x:c r="Q23" s="2"/>
+      <x:c r="R23" s="2"/>
+      <x:c r="S23" s="2"/>
+      <x:c r="T23" s="2"/>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="8" t="str">
@@ -3986,7 +4789,7 @@
         <x:v>한국수자원공사 우량수위 관측소 운영 정보</x:v>
       </x:c>
       <x:c r="C24" s="8" t="str">
-        <x:v>관측소별 수위·유량, 10분/30분/시간. 개발계정 1만 회.</x:v>
+        <x:v>관측소별 수위·유량, 10분/30분/시간. 개발 1만 회; 운영 증량 신청 가능, 고정 수치 미공개.</x:v>
       </x:c>
       <x:c r="D24" s="8" t="str">
         <x:v>https://www.data.go.kr/data/15099115/openapi.do</x:v>
@@ -4004,6 +4807,9 @@
       <x:c r="O24" s="2"/>
       <x:c r="P24" s="2"/>
       <x:c r="Q24" s="2"/>
+      <x:c r="R24" s="2"/>
+      <x:c r="S24" s="2"/>
+      <x:c r="T24" s="2"/>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="8" t="str">
@@ -4013,7 +4819,7 @@
         <x:v>한국수자원공사 수문 운영 정보</x:v>
       </x:c>
       <x:c r="C25" s="8" t="str">
-        <x:v>61개 댐·보 수위·유입량·방류량. 개발계정 1만 회.</x:v>
+        <x:v>61개 댐·보 수위·유입량·방류량. 개발 1만 회; 운영 증량 신청 가능, 고정 수치 미공개.</x:v>
       </x:c>
       <x:c r="D25" s="8" t="str">
         <x:v>https://www.data.go.kr/data/15099110/openapi.do</x:v>
@@ -4031,6 +4837,9 @@
       <x:c r="O25" s="2"/>
       <x:c r="P25" s="2"/>
       <x:c r="Q25" s="2"/>
+      <x:c r="R25" s="2"/>
+      <x:c r="S25" s="2"/>
+      <x:c r="T25" s="2"/>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="8" t="str">
@@ -4058,6 +4867,9 @@
       <x:c r="O26" s="2"/>
       <x:c r="P26" s="2"/>
       <x:c r="Q26" s="2"/>
+      <x:c r="R26" s="2"/>
+      <x:c r="S26" s="2"/>
+      <x:c r="T26" s="2"/>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="8" t="str">
@@ -4085,6 +4897,9 @@
       <x:c r="O27" s="2"/>
       <x:c r="P27" s="2"/>
       <x:c r="Q27" s="2"/>
+      <x:c r="R27" s="2"/>
+      <x:c r="S27" s="2"/>
+      <x:c r="T27" s="2"/>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="8" t="str">
@@ -4112,6 +4927,9 @@
       <x:c r="O28" s="2"/>
       <x:c r="P28" s="2"/>
       <x:c r="Q28" s="2"/>
+      <x:c r="R28" s="2"/>
+      <x:c r="S28" s="2"/>
+      <x:c r="T28" s="2"/>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="8" t="str">
@@ -4139,6 +4957,9 @@
       <x:c r="O29" s="2"/>
       <x:c r="P29" s="2"/>
       <x:c r="Q29" s="2"/>
+      <x:c r="R29" s="2"/>
+      <x:c r="S29" s="2"/>
+      <x:c r="T29" s="2"/>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="8" t="str">
@@ -4166,6 +4987,9 @@
       <x:c r="O30" s="2"/>
       <x:c r="P30" s="2"/>
       <x:c r="Q30" s="2"/>
+      <x:c r="R30" s="2"/>
+      <x:c r="S30" s="2"/>
+      <x:c r="T30" s="2"/>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="8" t="str">
@@ -4193,6 +5017,9 @@
       <x:c r="O31" s="2"/>
       <x:c r="P31" s="2"/>
       <x:c r="Q31" s="2"/>
+      <x:c r="R31" s="2"/>
+      <x:c r="S31" s="2"/>
+      <x:c r="T31" s="2"/>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="8" t="str">
@@ -4220,6 +5047,9 @@
       <x:c r="O32" s="2"/>
       <x:c r="P32" s="2"/>
       <x:c r="Q32" s="2"/>
+      <x:c r="R32" s="2"/>
+      <x:c r="S32" s="2"/>
+      <x:c r="T32" s="2"/>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="8" t="str">
@@ -4247,12 +5077,23 @@
       <x:c r="O33" s="2"/>
       <x:c r="P33" s="2"/>
       <x:c r="Q33" s="2"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="2"/>
-      <x:c r="B34" s="2"/>
-      <x:c r="C34" s="2"/>
-      <x:c r="D34" s="2"/>
+      <x:c r="R33" s="2"/>
+      <x:c r="S33" s="2"/>
+      <x:c r="T33" s="2"/>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="8" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="str">
+        <x:v>저장소 제공처별 예상 예산</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="str">
+        <x:v>현재 경로의 겨울 APIHub 필수 3.842GB, 재시도 예약 0.400GB를 공식 5GB와 비교.</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="str">
+        <x:v>docs/전체_수정사항_및_반영상태_20261010.md</x:v>
+      </x:c>
       <x:c r="E34" s="2"/>
       <x:c r="F34" s="2"/>
       <x:c r="G34" s="2"/>
@@ -4266,10 +5107,17 @@
       <x:c r="O34" s="2"/>
       <x:c r="P34" s="2"/>
       <x:c r="Q34" s="2"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
+      <x:c r="R34" s="2"/>
+      <x:c r="S34" s="2"/>
+      <x:c r="T34" s="2"/>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="8" t="str">
+        <x:v>구역 차이</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="str">
+        <x:v>API 지점·해수욕장·시설·광역 해역·해양모델 bbox는 기상청 nx/ny 5km 셀과 범위·해상도가 다르다. 위치를 셀에 연결하는 것은 셀 전체의 동일 실측값을 뜻하지 않는다.</x:v>
+      </x:c>
       <x:c r="C35" s="2"/>
       <x:c r="D35" s="2"/>
       <x:c r="E35" s="2"/>
@@ -4285,10 +5133,17 @@
       <x:c r="O35" s="2"/>
       <x:c r="P35" s="2"/>
       <x:c r="Q35" s="2"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="2"/>
-      <x:c r="B36" s="2"/>
+      <x:c r="R35" s="2"/>
+      <x:c r="S35" s="2"/>
+      <x:c r="T35" s="2"/>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="8" t="str">
+        <x:v>운영계정</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="str">
+        <x:v>K-water 해당 API는 운영단계 자동승인과 활용사례 등록 후 트래픽 증가 신청을 안내하지만 운영계정의 고정 일일 횟수는 공개하지 않는다. 실제 승인된 숫자를 입력해 판정해야 한다. 포털 운영계정과 APIHub 회원 등급은 별개다.</x:v>
+      </x:c>
       <x:c r="C36" s="2"/>
       <x:c r="D36" s="2"/>
       <x:c r="E36" s="2"/>
@@ -4304,10 +5159,17 @@
       <x:c r="O36" s="2"/>
       <x:c r="P36" s="2"/>
       <x:c r="Q36" s="2"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="2"/>
-      <x:c r="B37" s="2"/>
+      <x:c r="R36" s="2"/>
+      <x:c r="S36" s="2"/>
+      <x:c r="T36" s="2"/>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="8" t="str">
+        <x:v>한도 초과 대안</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>하천 100곳 10분 수집은 14,400회/일로 개발 10,000회 초과. 운영계정에서 최소 14,400회+페이지·재시도 여유를 승인받으면 가능. APIHub 낙뢰 2MB/회 가정은 공식 5GB 한도 내라 포털 운영계정 변경이 필요 없다.</x:v>
+      </x:c>
       <x:c r="C37" s="2"/>
       <x:c r="D37" s="2"/>
       <x:c r="E37" s="2"/>
@@ -4323,6 +5185,9 @@
       <x:c r="O37" s="2"/>
       <x:c r="P37" s="2"/>
       <x:c r="Q37" s="2"/>
+      <x:c r="R37" s="2"/>
+      <x:c r="S37" s="2"/>
+      <x:c r="T37" s="2"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2"/>
@@ -4342,12 +5207,23 @@
       <x:c r="O38" s="2"/>
       <x:c r="P38" s="2"/>
       <x:c r="Q38" s="2"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="2"/>
-      <x:c r="B39" s="2"/>
-      <x:c r="C39" s="2"/>
-      <x:c r="D39" s="2"/>
+      <x:c r="R38" s="2"/>
+      <x:c r="S38" s="2"/>
+      <x:c r="T38" s="2"/>
+    </x:row>
+    <x:row r="39" ht="55" customHeight="1">
+      <x:c r="A39" s="8" t="str">
+        <x:v>S19</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>부산광역시 해운대해수욕장</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>해변 길이 약 1.5km. 5km 격자 한 변과 비교하면 약 30%; 해변 위치와 실제 격자 경계의 중첩은 별도 확인 필요.</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="str">
+        <x:v>https://www.busan.go.kr/depart/ahhaewonndae</x:v>
+      </x:c>
       <x:c r="E39" s="2"/>
       <x:c r="F39" s="2"/>
       <x:c r="G39" s="2"/>
@@ -4361,12 +5237,23 @@
       <x:c r="O39" s="2"/>
       <x:c r="P39" s="2"/>
       <x:c r="Q39" s="2"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="2"/>
+      <x:c r="R39" s="2"/>
+      <x:c r="S39" s="2"/>
+      <x:c r="T39" s="2"/>
+    </x:row>
+    <x:row r="40" ht="55" customHeight="1">
+      <x:c r="A40" s="8" t="str">
+        <x:v>S20</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>기상청 속초 지역 기후특성</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>대청봉 해발 1,708m. 속초 관측소 고도와 비교한 높이 차이는 별도 S22를 함께 참고.</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="str">
+        <x:v>https://www.weather.go.kr/w/climate/statistics/region.do?area=2</x:v>
+      </x:c>
       <x:c r="E40" s="2"/>
       <x:c r="F40" s="2"/>
       <x:c r="G40" s="2"/>
@@ -4380,12 +5267,23 @@
       <x:c r="O40" s="2"/>
       <x:c r="P40" s="2"/>
       <x:c r="Q40" s="2"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
-      <x:c r="C41" s="2"/>
-      <x:c r="D41" s="2"/>
+      <x:c r="R40" s="2"/>
+      <x:c r="S40" s="2"/>
+      <x:c r="T40" s="2"/>
+    </x:row>
+    <x:row r="41" ht="55" customHeight="1">
+      <x:c r="A41" s="8" t="str">
+        <x:v>S21</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>K-water 수위관측소 현황</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>안동댐·안동댐방수로는 각각 등록된 관측 지점. 실제 우량수위 API 포함 여부와 지점코드는 활용 전 확인 필요.</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="str">
+        <x:v>https://www.kwater.or.kr/download/water/info_stat01.pdf</x:v>
+      </x:c>
       <x:c r="E41" s="2"/>
       <x:c r="F41" s="2"/>
       <x:c r="G41" s="2"/>
@@ -4399,12 +5297,23 @@
       <x:c r="O41" s="2"/>
       <x:c r="P41" s="2"/>
       <x:c r="Q41" s="2"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
-      <x:c r="C42" s="2"/>
-      <x:c r="D42" s="2"/>
+      <x:c r="R41" s="2"/>
+      <x:c r="S41" s="2"/>
+      <x:c r="T41" s="2"/>
+    </x:row>
+    <x:row r="42" ht="55" customHeight="1">
+      <x:c r="A42" s="8" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="str">
+        <x:v>기상청 지역별 상세관측</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="str">
+        <x:v>속초 ASOS 관측소의 해발고도 약 18m. 대청봉과의 높이 차이는 관측 환경 차이를 보여주는 예시다.</x:v>
+      </x:c>
+      <x:c r="D42" s="8" t="str">
+        <x:v>https://www.weather.go.kr/w/weather/land/aws-obs.do?config=&amp;db=MINDB_01M&amp;sidoCode=asos&amp;sort=&amp;stnId=0&amp;tm=</x:v>
+      </x:c>
       <x:c r="E42" s="2"/>
       <x:c r="F42" s="2"/>
       <x:c r="G42" s="2"/>
@@ -4418,10 +5327,17 @@
       <x:c r="O42" s="2"/>
       <x:c r="P42" s="2"/>
       <x:c r="Q42" s="2"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
+      <x:c r="R42" s="2"/>
+      <x:c r="S42" s="2"/>
+      <x:c r="T42" s="2"/>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="8" t="str">
+        <x:v>면적 비교 주의</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="str">
+        <x:v>5×5km≈25㎢는 격자 규모의 대략값이다. 점·하천 단면 관측에는 같은 의미의 면적이 없으므로 면적 배수를 계산하지 않는다. 해운대 30%는 해변 길이와 격자 한 변만 비교한 값이다.</x:v>
+      </x:c>
       <x:c r="C43" s="2"/>
       <x:c r="D43" s="2"/>
       <x:c r="E43" s="2"/>
@@ -4437,6 +5353,9 @@
       <x:c r="O43" s="2"/>
       <x:c r="P43" s="2"/>
       <x:c r="Q43" s="2"/>
+      <x:c r="R43" s="2"/>
+      <x:c r="S43" s="2"/>
+      <x:c r="T43" s="2"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2"/>
@@ -4456,6 +5375,9 @@
       <x:c r="O44" s="2"/>
       <x:c r="P44" s="2"/>
       <x:c r="Q44" s="2"/>
+      <x:c r="R44" s="2"/>
+      <x:c r="S44" s="2"/>
+      <x:c r="T44" s="2"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2"/>
@@ -4475,6 +5397,9 @@
       <x:c r="O45" s="2"/>
       <x:c r="P45" s="2"/>
       <x:c r="Q45" s="2"/>
+      <x:c r="R45" s="2"/>
+      <x:c r="S45" s="2"/>
+      <x:c r="T45" s="2"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2"/>
@@ -4494,6 +5419,9 @@
       <x:c r="O46" s="2"/>
       <x:c r="P46" s="2"/>
       <x:c r="Q46" s="2"/>
+      <x:c r="R46" s="2"/>
+      <x:c r="S46" s="2"/>
+      <x:c r="T46" s="2"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2"/>
@@ -4513,6 +5441,9 @@
       <x:c r="O47" s="2"/>
       <x:c r="P47" s="2"/>
       <x:c r="Q47" s="2"/>
+      <x:c r="R47" s="2"/>
+      <x:c r="S47" s="2"/>
+      <x:c r="T47" s="2"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2"/>
@@ -4532,6 +5463,9 @@
       <x:c r="O48" s="2"/>
       <x:c r="P48" s="2"/>
       <x:c r="Q48" s="2"/>
+      <x:c r="R48" s="2"/>
+      <x:c r="S48" s="2"/>
+      <x:c r="T48" s="2"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2"/>
@@ -4551,6 +5485,9 @@
       <x:c r="O49" s="2"/>
       <x:c r="P49" s="2"/>
       <x:c r="Q49" s="2"/>
+      <x:c r="R49" s="2"/>
+      <x:c r="S49" s="2"/>
+      <x:c r="T49" s="2"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2"/>
@@ -4570,6 +5507,9 @@
       <x:c r="O50" s="2"/>
       <x:c r="P50" s="2"/>
       <x:c r="Q50" s="2"/>
+      <x:c r="R50" s="2"/>
+      <x:c r="S50" s="2"/>
+      <x:c r="T50" s="2"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2"/>
@@ -4589,6 +5529,9 @@
       <x:c r="O51" s="2"/>
       <x:c r="P51" s="2"/>
       <x:c r="Q51" s="2"/>
+      <x:c r="R51" s="2"/>
+      <x:c r="S51" s="2"/>
+      <x:c r="T51" s="2"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2"/>
@@ -4608,6 +5551,9 @@
       <x:c r="O52" s="2"/>
       <x:c r="P52" s="2"/>
       <x:c r="Q52" s="2"/>
+      <x:c r="R52" s="2"/>
+      <x:c r="S52" s="2"/>
+      <x:c r="T52" s="2"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2"/>
@@ -4627,6 +5573,9 @@
       <x:c r="O53" s="2"/>
       <x:c r="P53" s="2"/>
       <x:c r="Q53" s="2"/>
+      <x:c r="R53" s="2"/>
+      <x:c r="S53" s="2"/>
+      <x:c r="T53" s="2"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2"/>
@@ -4646,6 +5595,9 @@
       <x:c r="O54" s="2"/>
       <x:c r="P54" s="2"/>
       <x:c r="Q54" s="2"/>
+      <x:c r="R54" s="2"/>
+      <x:c r="S54" s="2"/>
+      <x:c r="T54" s="2"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2"/>
@@ -4665,6 +5617,9 @@
       <x:c r="O55" s="2"/>
       <x:c r="P55" s="2"/>
       <x:c r="Q55" s="2"/>
+      <x:c r="R55" s="2"/>
+      <x:c r="S55" s="2"/>
+      <x:c r="T55" s="2"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2"/>
@@ -4684,6 +5639,9 @@
       <x:c r="O56" s="2"/>
       <x:c r="P56" s="2"/>
       <x:c r="Q56" s="2"/>
+      <x:c r="R56" s="2"/>
+      <x:c r="S56" s="2"/>
+      <x:c r="T56" s="2"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2"/>
@@ -4703,6 +5661,9 @@
       <x:c r="O57" s="2"/>
       <x:c r="P57" s="2"/>
       <x:c r="Q57" s="2"/>
+      <x:c r="R57" s="2"/>
+      <x:c r="S57" s="2"/>
+      <x:c r="T57" s="2"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2"/>
@@ -4722,6 +5683,9 @@
       <x:c r="O58" s="2"/>
       <x:c r="P58" s="2"/>
       <x:c r="Q58" s="2"/>
+      <x:c r="R58" s="2"/>
+      <x:c r="S58" s="2"/>
+      <x:c r="T58" s="2"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2"/>
@@ -4741,6 +5705,9 @@
       <x:c r="O59" s="2"/>
       <x:c r="P59" s="2"/>
       <x:c r="Q59" s="2"/>
+      <x:c r="R59" s="2"/>
+      <x:c r="S59" s="2"/>
+      <x:c r="T59" s="2"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2"/>
@@ -4760,6 +5727,9 @@
       <x:c r="O60" s="2"/>
       <x:c r="P60" s="2"/>
       <x:c r="Q60" s="2"/>
+      <x:c r="R60" s="2"/>
+      <x:c r="S60" s="2"/>
+      <x:c r="T60" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
